--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17T02:00:37.393929+00:00</t>
+          <t>2026-08-28T13:31:58.420547+00:00</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>15000</v>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6600000</v>
+        <v>6720000</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>4400</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="3">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>250000</v>
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>110000000</v>
+        <v>112000000</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>73333.33</v>
+        <v>74666.67</v>
       </c>
     </row>
     <row r="4">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>750000</v>
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>330000000</v>
+        <v>336000000</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>220000</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>50000</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>11000000</v>
+        <v>11200000</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>7333.33</v>
+        <v>7466.67</v>
       </c>
     </row>
     <row r="6">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>15000</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1050000</v>
+        <v>1170000</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>250000</v>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>17500000</v>
+        <v>19500000</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>11666.67</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="8">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>750000</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>52500000</v>
+        <v>58500000</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>35000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="9">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>50000</v>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1750000</v>
+        <v>1950000</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1166.67</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="10">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>15000</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>450000</v>
+        <v>480000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>250000</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7500000</v>
+        <v>8000000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5000</v>
+        <v>5333.33</v>
       </c>
     </row>
     <row r="12">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>750000</v>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>22500000</v>
+        <v>24000000</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>50000</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>750000</v>
+        <v>800000</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>500</v>
+        <v>533.33</v>
       </c>
     </row>
     <row r="14">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>15000</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9420000</v>
+        <v>9510000</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>6280</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="15">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>250000</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>157000000</v>
+        <v>158500000</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>104666.67</v>
+        <v>105666.67</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>750000</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>471000000</v>
+        <v>475500000</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>314000</v>
+        <v>317000</v>
       </c>
     </row>
     <row r="17">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>50000</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>15700000</v>
+        <v>15850000</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>10466.67</v>
+        <v>10566.67</v>
       </c>
     </row>
     <row r="18">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>15000</v>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>10410000</v>
+        <v>10440000</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>6940</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="27">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>250000</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>173500000</v>
+        <v>174000000</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>115666.67</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="28">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>750000</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>520500000</v>
+        <v>522000000</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>347000</v>
+        <v>348000</v>
       </c>
     </row>
     <row r="29">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>50000</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>17350000</v>
+        <v>17400000</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>11566.67</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="30">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>15000</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>10590000</v>
+        <v>10620000</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>7060</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="39">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>250000</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>176500000</v>
+        <v>177000000</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>117666.67</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="40">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>750000</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>529500000</v>
+        <v>531000000</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>353000</v>
+        <v>354000</v>
       </c>
     </row>
     <row r="41">
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>50000</v>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>17650000</v>
+        <v>17700000</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>11766.67</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="42">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>15000</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>10800000</v>
+        <v>10830000</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>7200</v>
+        <v>7220</v>
       </c>
     </row>
     <row r="51">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>250000</v>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>180000000</v>
+        <v>180500000</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>120000</v>
+        <v>120333.33</v>
       </c>
     </row>
     <row r="52">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>750000</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>540000000</v>
+        <v>541500000</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>360000</v>
+        <v>361000</v>
       </c>
     </row>
     <row r="53">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>50000</v>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>18000000</v>
+        <v>18050000</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>12000</v>
+        <v>12033.33</v>
       </c>
     </row>
     <row r="54">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>15000</v>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>11550000</v>
+        <v>11580000</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>7700</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="63">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>250000</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>192500000</v>
+        <v>193000000</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>128333.33</v>
+        <v>128666.67</v>
       </c>
     </row>
     <row r="64">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>750000</v>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>577500000</v>
+        <v>579000000</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>385000</v>
+        <v>386000</v>
       </c>
     </row>
     <row r="65">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>50000</v>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>19250000</v>
+        <v>19300000</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>12833.33</v>
+        <v>12866.67</v>
       </c>
     </row>
     <row r="66">
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E74" s="6" t="n">
         <v>15000</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="G74" s="6" t="n">
-        <v>12210000</v>
+        <v>12240000</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>8140</v>
+        <v>8160</v>
       </c>
     </row>
     <row r="75">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>250000</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="G75" s="6" t="n">
-        <v>203500000</v>
+        <v>204000000</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>135666.67</v>
+        <v>136000</v>
       </c>
     </row>
     <row r="76">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>750000</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="G76" s="6" t="n">
-        <v>610500000</v>
+        <v>612000000</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>407000</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="77">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>50000</v>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="G77" s="6" t="n">
-        <v>20350000</v>
+        <v>20400000</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>13566.67</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="78">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>15000</v>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="G86" s="6" t="n">
-        <v>12570000</v>
+        <v>12600000</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>8380</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="87">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>250000</v>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>209500000</v>
+        <v>210000000</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>139666.67</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="88">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>750000</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>628500000</v>
+        <v>630000000</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>419000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="89">
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>50000</v>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>20950000</v>
+        <v>21000000</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>13966.67</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="90">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E98" s="6" t="n">
         <v>15000</v>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>12750000</v>
+        <v>12780000</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>8500</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="99">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>250000</v>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="G99" s="6" t="n">
-        <v>212500000</v>
+        <v>213000000</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>141666.67</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="100">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>750000</v>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="G100" s="6" t="n">
-        <v>637500000</v>
+        <v>639000000</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>425000</v>
+        <v>426000</v>
       </c>
     </row>
     <row r="101">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>50000</v>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>21250000</v>
+        <v>21300000</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>14166.67</v>
+        <v>14200</v>
       </c>
     </row>
     <row r="102">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E110" s="6" t="n">
         <v>15000</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>13020000</v>
+        <v>13050000</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>8680</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="111">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E111" s="6" t="n">
         <v>250000</v>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="G111" s="6" t="n">
-        <v>217000000</v>
+        <v>217500000</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>144666.67</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="112">
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E112" s="6" t="n">
         <v>750000</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="G112" s="6" t="n">
-        <v>651000000</v>
+        <v>652500000</v>
       </c>
       <c r="H112" s="7" t="n">
-        <v>434000</v>
+        <v>435000</v>
       </c>
     </row>
     <row r="113">
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E113" s="6" t="n">
         <v>50000</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="G113" s="6" t="n">
-        <v>21700000</v>
+        <v>21750000</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>14466.67</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="114">
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="D278" s="6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E278" s="6" t="n">
         <v>15000</v>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="G278" s="6" t="n">
-        <v>15360000</v>
+        <v>15390000</v>
       </c>
       <c r="H278" s="7" t="n">
-        <v>10240</v>
+        <v>10260</v>
       </c>
     </row>
     <row r="279">
@@ -10039,7 +10039,7 @@
         </is>
       </c>
       <c r="D279" s="6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E279" s="6" t="n">
         <v>250000</v>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="G279" s="6" t="n">
-        <v>256000000</v>
+        <v>256500000</v>
       </c>
       <c r="H279" s="7" t="n">
-        <v>170666.67</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="280">
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="D280" s="6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E280" s="6" t="n">
         <v>750000</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="G280" s="6" t="n">
-        <v>768000000</v>
+        <v>769500000</v>
       </c>
       <c r="H280" s="7" t="n">
-        <v>512000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="281">
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="D281" s="6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E281" s="6" t="n">
         <v>50000</v>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="G281" s="6" t="n">
-        <v>25600000</v>
+        <v>25650000</v>
       </c>
       <c r="H281" s="7" t="n">
-        <v>17066.67</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="282">
@@ -13314,13 +13314,13 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>457600000</v>
+        <v>465920000</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>305066.66</v>
+        <v>310613.34</v>
       </c>
     </row>
     <row r="3">
@@ -13335,13 +13335,13 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>72800000</v>
+        <v>81120000</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>48533.34</v>
+        <v>54080</v>
       </c>
     </row>
     <row r="4">
@@ -13356,13 +13356,13 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>31200000</v>
+        <v>33280000</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>20800</v>
+        <v>22186.66</v>
       </c>
     </row>
     <row r="5">
@@ -13377,13 +13377,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>653120000</v>
+        <v>659360000</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>435413.34</v>
+        <v>439573.34</v>
       </c>
     </row>
     <row r="6">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>721760000</v>
+        <v>723840000</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>481173.34</v>
+        <v>482560</v>
       </c>
     </row>
     <row r="9">
@@ -13503,13 +13503,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>734240000</v>
+        <v>736320000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>489493.34</v>
+        <v>490880</v>
       </c>
     </row>
     <row r="12">
@@ -13566,13 +13566,13 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>748800000</v>
+        <v>750880000</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>499200</v>
+        <v>500586.66</v>
       </c>
     </row>
     <row r="15">
@@ -13629,13 +13629,13 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>800800000</v>
+        <v>802880000</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>533866.66</v>
+        <v>535253.34</v>
       </c>
     </row>
     <row r="18">
@@ -13692,13 +13692,13 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>846560000</v>
+        <v>848640000</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>564373.34</v>
+        <v>565760</v>
       </c>
     </row>
     <row r="21">
@@ -13755,13 +13755,13 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>871520000</v>
+        <v>873600000</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>581013.34</v>
+        <v>582400</v>
       </c>
     </row>
     <row r="24">
@@ -13818,13 +13818,13 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>884000000</v>
+        <v>886080000</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>589333.34</v>
+        <v>590720</v>
       </c>
     </row>
     <row r="27">
@@ -13881,13 +13881,13 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>902720000</v>
+        <v>904800000</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>601813.34</v>
+        <v>603200</v>
       </c>
     </row>
     <row r="30">
@@ -14763,13 +14763,13 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1064960000</v>
+        <v>1067040000</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>709973.34</v>
+        <v>711360</v>
       </c>
     </row>
     <row r="72">

--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T13:31:58.420547+00:00</t>
+          <t>2026-08-28T18:49:53.220713+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T18:49:53.220713+00:00</t>
+          <t>2026-08-28T20:13:47.903954+00:00</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>15000</v>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6720000</v>
+        <v>6780000</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>4480</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="3">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>250000</v>
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>112000000</v>
+        <v>113000000</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>74666.67</v>
+        <v>75333.33</v>
       </c>
     </row>
     <row r="4">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>750000</v>
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>336000000</v>
+        <v>339000000</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>224000</v>
+        <v>226000</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>50000</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>11200000</v>
+        <v>11300000</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>7466.67</v>
+        <v>7533.33</v>
       </c>
     </row>
     <row r="6">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>15000</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1170000</v>
+        <v>1200000</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>250000</v>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>19500000</v>
+        <v>20000000</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>13000</v>
+        <v>13333.33</v>
       </c>
     </row>
     <row r="8">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>750000</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>58500000</v>
+        <v>60000000</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>39000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="9">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>50000</v>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1950000</v>
+        <v>2000000</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1300</v>
+        <v>1333.33</v>
       </c>
     </row>
     <row r="10">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>15000</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>480000</v>
+        <v>510000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>250000</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>8000000</v>
+        <v>8500000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5333.33</v>
+        <v>5666.67</v>
       </c>
     </row>
     <row r="12">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>750000</v>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>24000000</v>
+        <v>25500000</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>16000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>50000</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>800000</v>
+        <v>850000</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>533.33</v>
+        <v>566.67</v>
       </c>
     </row>
     <row r="14">
@@ -13314,13 +13314,13 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>465920000</v>
+        <v>470080000</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>310613.34</v>
+        <v>313386.66</v>
       </c>
     </row>
     <row r="3">
@@ -13335,13 +13335,13 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>81120000</v>
+        <v>83200000</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>54080</v>
+        <v>55466.66</v>
       </c>
     </row>
     <row r="4">
@@ -13356,13 +13356,13 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>33280000</v>
+        <v>35360000</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>22186.66</v>
+        <v>23573.34</v>
       </c>
     </row>
     <row r="5">

--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T20:13:47.903954+00:00</t>
+          <t>2026-08-31T23:48:51.976270+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31T23:48:51.976270+00:00</t>
+          <t>2026-09-01T00:10:26.191025+00:00</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>15000</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>1260000</v>
+        <v>1230000</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="59">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>250000</v>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>21000000</v>
+        <v>20500000</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>14000</v>
+        <v>13666.67</v>
       </c>
     </row>
     <row r="60">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>750000</v>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>63000000</v>
+        <v>61500000</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>42000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="61">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>50000</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>2100000</v>
+        <v>2050000</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>1400</v>
+        <v>1366.67</v>
       </c>
     </row>
     <row r="62">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>15000</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="G70" s="6" t="n">
-        <v>1320000</v>
+        <v>1290000</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>880</v>
+        <v>860</v>
       </c>
     </row>
     <row r="71">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>250000</v>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>22000000</v>
+        <v>21500000</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>14666.67</v>
+        <v>14333.33</v>
       </c>
     </row>
     <row r="72">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>750000</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>66000000</v>
+        <v>64500000</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>44000</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="73">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>50000</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="G73" s="6" t="n">
-        <v>2200000</v>
+        <v>2150000</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>1466.67</v>
+        <v>1433.33</v>
       </c>
     </row>
     <row r="74">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>15000</v>
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="G82" s="6" t="n">
-        <v>1410000</v>
+        <v>1380000</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="83">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>250000</v>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="G83" s="6" t="n">
-        <v>23500000</v>
+        <v>23000000</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>15666.67</v>
+        <v>15333.33</v>
       </c>
     </row>
     <row r="84">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>750000</v>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="G84" s="6" t="n">
-        <v>70500000</v>
+        <v>69000000</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>47000</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="85">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>50000</v>
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="G85" s="6" t="n">
-        <v>2350000</v>
+        <v>2300000</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>1566.67</v>
+        <v>1533.33</v>
       </c>
     </row>
     <row r="86">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E94" s="6" t="n">
         <v>15000</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1410000</v>
+        <v>1380000</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="95">
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E95" s="6" t="n">
         <v>250000</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>23500000</v>
+        <v>23000000</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>15666.67</v>
+        <v>15333.33</v>
       </c>
     </row>
     <row r="96">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E96" s="6" t="n">
         <v>750000</v>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>70500000</v>
+        <v>69000000</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>47000</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="97">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E97" s="6" t="n">
         <v>50000</v>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>2350000</v>
+        <v>2300000</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>1566.67</v>
+        <v>1533.33</v>
       </c>
     </row>
     <row r="98">
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>15000</v>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="G106" s="6" t="n">
-        <v>1440000</v>
+        <v>1410000</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
     </row>
     <row r="107">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>250000</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="G107" s="6" t="n">
-        <v>24000000</v>
+        <v>23500000</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>16000</v>
+        <v>15666.67</v>
       </c>
     </row>
     <row r="108">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E108" s="6" t="n">
         <v>750000</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>72000000</v>
+        <v>70500000</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>48000</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="109">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>50000</v>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="G109" s="6" t="n">
-        <v>2400000</v>
+        <v>2350000</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>1600</v>
+        <v>1566.67</v>
       </c>
     </row>
     <row r="110">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>15000</v>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="G118" s="6" t="n">
-        <v>1500000</v>
+        <v>1470000</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
     </row>
     <row r="119">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E119" s="6" t="n">
         <v>250000</v>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="G119" s="6" t="n">
-        <v>25000000</v>
+        <v>24500000</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>16666.67</v>
+        <v>16333.33</v>
       </c>
     </row>
     <row r="120">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E120" s="6" t="n">
         <v>750000</v>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="G120" s="6" t="n">
-        <v>75000000</v>
+        <v>73500000</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>50000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="121">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E121" s="6" t="n">
         <v>50000</v>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="G121" s="6" t="n">
-        <v>2500000</v>
+        <v>2450000</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>1666.67</v>
+        <v>1633.33</v>
       </c>
     </row>
     <row r="122">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E130" s="6" t="n">
         <v>15000</v>
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="G130" s="6" t="n">
-        <v>1560000</v>
+        <v>1530000</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>1040</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="131">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>250000</v>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="G131" s="6" t="n">
-        <v>26000000</v>
+        <v>25500000</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>17333.33</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="132">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E132" s="6" t="n">
         <v>750000</v>
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="G132" s="6" t="n">
-        <v>78000000</v>
+        <v>76500000</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>52000</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="133">
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E133" s="6" t="n">
         <v>50000</v>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="G133" s="6" t="n">
-        <v>2600000</v>
+        <v>2550000</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>1733.33</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="134">
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E142" s="6" t="n">
         <v>15000</v>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="G142" s="6" t="n">
-        <v>1650000</v>
+        <v>1620000</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="143">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>250000</v>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="G143" s="6" t="n">
-        <v>27500000</v>
+        <v>27000000</v>
       </c>
       <c r="H143" s="7" t="n">
-        <v>18333.33</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="144">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>750000</v>
@@ -5460,10 +5460,10 @@
         </is>
       </c>
       <c r="G144" s="6" t="n">
-        <v>82500000</v>
+        <v>81000000</v>
       </c>
       <c r="H144" s="7" t="n">
-        <v>55000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="145">
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E145" s="6" t="n">
         <v>50000</v>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="G145" s="6" t="n">
-        <v>2750000</v>
+        <v>2700000</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>1833.33</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="146">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E154" s="6" t="n">
         <v>15000</v>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="G154" s="6" t="n">
-        <v>1650000</v>
+        <v>1620000</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="155">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E155" s="6" t="n">
         <v>250000</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="G155" s="6" t="n">
-        <v>27500000</v>
+        <v>27000000</v>
       </c>
       <c r="H155" s="7" t="n">
-        <v>18333.33</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="156">
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E156" s="6" t="n">
         <v>750000</v>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="G156" s="6" t="n">
-        <v>82500000</v>
+        <v>81000000</v>
       </c>
       <c r="H156" s="7" t="n">
-        <v>55000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="157">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E157" s="6" t="n">
         <v>50000</v>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="G157" s="6" t="n">
-        <v>2750000</v>
+        <v>2700000</v>
       </c>
       <c r="H157" s="7" t="n">
-        <v>1833.33</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="158">
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E166" s="6" t="n">
         <v>15000</v>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="G166" s="6" t="n">
-        <v>1770000</v>
+        <v>1740000</v>
       </c>
       <c r="H166" s="7" t="n">
-        <v>1180</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="167">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E167" s="6" t="n">
         <v>250000</v>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="G167" s="6" t="n">
-        <v>29500000</v>
+        <v>29000000</v>
       </c>
       <c r="H167" s="7" t="n">
-        <v>19666.67</v>
+        <v>19333.33</v>
       </c>
     </row>
     <row r="168">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E168" s="6" t="n">
         <v>750000</v>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="G168" s="6" t="n">
-        <v>88500000</v>
+        <v>87000000</v>
       </c>
       <c r="H168" s="7" t="n">
-        <v>59000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="169">
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E169" s="6" t="n">
         <v>50000</v>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="G169" s="6" t="n">
-        <v>2950000</v>
+        <v>2900000</v>
       </c>
       <c r="H169" s="7" t="n">
-        <v>1966.67</v>
+        <v>1933.33</v>
       </c>
     </row>
     <row r="170">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="D178" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E178" s="6" t="n">
         <v>15000</v>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="G178" s="6" t="n">
-        <v>1770000</v>
+        <v>1740000</v>
       </c>
       <c r="H178" s="7" t="n">
-        <v>1180</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="179">
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="D179" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E179" s="6" t="n">
         <v>250000</v>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="G179" s="6" t="n">
-        <v>29500000</v>
+        <v>29000000</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>19666.67</v>
+        <v>19333.33</v>
       </c>
     </row>
     <row r="180">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="D180" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E180" s="6" t="n">
         <v>750000</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="G180" s="6" t="n">
-        <v>88500000</v>
+        <v>87000000</v>
       </c>
       <c r="H180" s="7" t="n">
-        <v>59000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="181">
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="D181" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E181" s="6" t="n">
         <v>50000</v>
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="G181" s="6" t="n">
-        <v>2950000</v>
+        <v>2900000</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>1966.67</v>
+        <v>1933.33</v>
       </c>
     </row>
     <row r="182">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="D190" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E190" s="6" t="n">
         <v>15000</v>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="G190" s="6" t="n">
-        <v>1740000</v>
+        <v>1710000</v>
       </c>
       <c r="H190" s="7" t="n">
-        <v>1160</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="191">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="D191" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E191" s="6" t="n">
         <v>250000</v>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="G191" s="6" t="n">
-        <v>29000000</v>
+        <v>28500000</v>
       </c>
       <c r="H191" s="7" t="n">
-        <v>19333.33</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="192">
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="D192" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E192" s="6" t="n">
         <v>750000</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="G192" s="6" t="n">
-        <v>87000000</v>
+        <v>85500000</v>
       </c>
       <c r="H192" s="7" t="n">
-        <v>58000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="193">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="D193" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E193" s="6" t="n">
         <v>50000</v>
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="G193" s="6" t="n">
-        <v>2900000</v>
+        <v>2850000</v>
       </c>
       <c r="H193" s="7" t="n">
-        <v>1933.33</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="194">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="D202" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E202" s="6" t="n">
         <v>15000</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="G202" s="6" t="n">
-        <v>1830000</v>
+        <v>1800000</v>
       </c>
       <c r="H202" s="7" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="203">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="D203" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E203" s="6" t="n">
         <v>250000</v>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="G203" s="6" t="n">
-        <v>30500000</v>
+        <v>30000000</v>
       </c>
       <c r="H203" s="7" t="n">
-        <v>20333.33</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="204">
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="D204" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E204" s="6" t="n">
         <v>750000</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="G204" s="6" t="n">
-        <v>91500000</v>
+        <v>90000000</v>
       </c>
       <c r="H204" s="7" t="n">
-        <v>61000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="205">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="D205" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E205" s="6" t="n">
         <v>50000</v>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="G205" s="6" t="n">
-        <v>3050000</v>
+        <v>3000000</v>
       </c>
       <c r="H205" s="7" t="n">
-        <v>2033.33</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="206">
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="D214" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E214" s="6" t="n">
         <v>15000</v>
@@ -7840,10 +7840,10 @@
         </is>
       </c>
       <c r="G214" s="6" t="n">
-        <v>1890000</v>
+        <v>1860000</v>
       </c>
       <c r="H214" s="7" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="215">
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="D215" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E215" s="6" t="n">
         <v>250000</v>
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="G215" s="6" t="n">
-        <v>31500000</v>
+        <v>31000000</v>
       </c>
       <c r="H215" s="7" t="n">
-        <v>21000</v>
+        <v>20666.67</v>
       </c>
     </row>
     <row r="216">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="D216" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E216" s="6" t="n">
         <v>750000</v>
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="G216" s="6" t="n">
-        <v>94500000</v>
+        <v>93000000</v>
       </c>
       <c r="H216" s="7" t="n">
-        <v>63000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="217">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="D217" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E217" s="6" t="n">
         <v>50000</v>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="G217" s="6" t="n">
-        <v>3150000</v>
+        <v>3100000</v>
       </c>
       <c r="H217" s="7" t="n">
-        <v>2100</v>
+        <v>2066.67</v>
       </c>
     </row>
     <row r="218">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="D226" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E226" s="6" t="n">
         <v>15000</v>
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="G226" s="6" t="n">
-        <v>1890000</v>
+        <v>1860000</v>
       </c>
       <c r="H226" s="7" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="227">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="D227" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E227" s="6" t="n">
         <v>250000</v>
@@ -8282,10 +8282,10 @@
         </is>
       </c>
       <c r="G227" s="6" t="n">
-        <v>31500000</v>
+        <v>31000000</v>
       </c>
       <c r="H227" s="7" t="n">
-        <v>21000</v>
+        <v>20666.67</v>
       </c>
     </row>
     <row r="228">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="D228" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E228" s="6" t="n">
         <v>750000</v>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="G228" s="6" t="n">
-        <v>94500000</v>
+        <v>93000000</v>
       </c>
       <c r="H228" s="7" t="n">
-        <v>63000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="229">
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="D229" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E229" s="6" t="n">
         <v>50000</v>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="G229" s="6" t="n">
-        <v>3150000</v>
+        <v>3100000</v>
       </c>
       <c r="H229" s="7" t="n">
-        <v>2100</v>
+        <v>2066.67</v>
       </c>
     </row>
     <row r="230">
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="D238" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E238" s="6" t="n">
         <v>15000</v>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="G238" s="6" t="n">
-        <v>1890000</v>
+        <v>1860000</v>
       </c>
       <c r="H238" s="7" t="n">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="239">
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="D239" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E239" s="6" t="n">
         <v>250000</v>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="G239" s="6" t="n">
-        <v>31500000</v>
+        <v>31000000</v>
       </c>
       <c r="H239" s="7" t="n">
-        <v>21000</v>
+        <v>20666.67</v>
       </c>
     </row>
     <row r="240">
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="D240" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E240" s="6" t="n">
         <v>750000</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="G240" s="6" t="n">
-        <v>94500000</v>
+        <v>93000000</v>
       </c>
       <c r="H240" s="7" t="n">
-        <v>63000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="241">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="D241" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E241" s="6" t="n">
         <v>50000</v>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="G241" s="6" t="n">
-        <v>3150000</v>
+        <v>3100000</v>
       </c>
       <c r="H241" s="7" t="n">
-        <v>2100</v>
+        <v>2066.67</v>
       </c>
     </row>
     <row r="242">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="D250" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E250" s="6" t="n">
         <v>15000</v>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="G250" s="6" t="n">
-        <v>2070000</v>
+        <v>2040000</v>
       </c>
       <c r="H250" s="7" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="251">
@@ -9087,7 +9087,7 @@
         </is>
       </c>
       <c r="D251" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E251" s="6" t="n">
         <v>250000</v>
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="G251" s="6" t="n">
-        <v>34500000</v>
+        <v>34000000</v>
       </c>
       <c r="H251" s="7" t="n">
-        <v>23000</v>
+        <v>22666.67</v>
       </c>
     </row>
     <row r="252">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="D252" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E252" s="6" t="n">
         <v>750000</v>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="G252" s="6" t="n">
-        <v>103500000</v>
+        <v>102000000</v>
       </c>
       <c r="H252" s="7" t="n">
-        <v>69000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="253">
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="D253" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E253" s="6" t="n">
         <v>50000</v>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="G253" s="6" t="n">
-        <v>3450000</v>
+        <v>3400000</v>
       </c>
       <c r="H253" s="7" t="n">
-        <v>2300</v>
+        <v>2266.67</v>
       </c>
     </row>
     <row r="254">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="D262" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E262" s="6" t="n">
         <v>15000</v>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="G262" s="6" t="n">
-        <v>2070000</v>
+        <v>2040000</v>
       </c>
       <c r="H262" s="7" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="263">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="D263" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E263" s="6" t="n">
         <v>250000</v>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="G263" s="6" t="n">
-        <v>34500000</v>
+        <v>34000000</v>
       </c>
       <c r="H263" s="7" t="n">
-        <v>23000</v>
+        <v>22666.67</v>
       </c>
     </row>
     <row r="264">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="D264" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E264" s="6" t="n">
         <v>750000</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="G264" s="6" t="n">
-        <v>103500000</v>
+        <v>102000000</v>
       </c>
       <c r="H264" s="7" t="n">
-        <v>69000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="265">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="D265" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E265" s="6" t="n">
         <v>50000</v>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="G265" s="6" t="n">
-        <v>3450000</v>
+        <v>3400000</v>
       </c>
       <c r="H265" s="7" t="n">
-        <v>2300</v>
+        <v>2266.67</v>
       </c>
     </row>
     <row r="266">
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="D274" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E274" s="6" t="n">
         <v>15000</v>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="G274" s="6" t="n">
-        <v>2130000</v>
+        <v>2100000</v>
       </c>
       <c r="H274" s="7" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="275">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="D275" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E275" s="6" t="n">
         <v>250000</v>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="G275" s="6" t="n">
-        <v>35500000</v>
+        <v>35000000</v>
       </c>
       <c r="H275" s="7" t="n">
-        <v>23666.67</v>
+        <v>23333.33</v>
       </c>
     </row>
     <row r="276">
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="D276" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E276" s="6" t="n">
         <v>750000</v>
@@ -9948,10 +9948,10 @@
         </is>
       </c>
       <c r="G276" s="6" t="n">
-        <v>106500000</v>
+        <v>105000000</v>
       </c>
       <c r="H276" s="7" t="n">
-        <v>71000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="277">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="D277" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E277" s="6" t="n">
         <v>50000</v>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="G277" s="6" t="n">
-        <v>3550000</v>
+        <v>3500000</v>
       </c>
       <c r="H277" s="7" t="n">
-        <v>2366.67</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="278">
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="D286" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E286" s="6" t="n">
         <v>15000</v>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="G286" s="6" t="n">
-        <v>2160000</v>
+        <v>2130000</v>
       </c>
       <c r="H286" s="7" t="n">
-        <v>1440</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="287">
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="D287" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E287" s="6" t="n">
         <v>250000</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="G287" s="6" t="n">
-        <v>36000000</v>
+        <v>35500000</v>
       </c>
       <c r="H287" s="7" t="n">
-        <v>24000</v>
+        <v>23666.67</v>
       </c>
     </row>
     <row r="288">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="D288" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E288" s="6" t="n">
         <v>750000</v>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="G288" s="6" t="n">
-        <v>108000000</v>
+        <v>106500000</v>
       </c>
       <c r="H288" s="7" t="n">
-        <v>72000</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="289">
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="D289" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E289" s="6" t="n">
         <v>50000</v>
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="G289" s="6" t="n">
-        <v>3600000</v>
+        <v>3550000</v>
       </c>
       <c r="H289" s="7" t="n">
-        <v>2400</v>
+        <v>2366.67</v>
       </c>
     </row>
     <row r="290">
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="D298" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E298" s="6" t="n">
         <v>15000</v>
@@ -10696,10 +10696,10 @@
         </is>
       </c>
       <c r="G298" s="6" t="n">
-        <v>2220000</v>
+        <v>2190000</v>
       </c>
       <c r="H298" s="7" t="n">
-        <v>1480</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="299">
@@ -10719,7 +10719,7 @@
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E299" s="6" t="n">
         <v>250000</v>
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="G299" s="6" t="n">
-        <v>37000000</v>
+        <v>36500000</v>
       </c>
       <c r="H299" s="7" t="n">
-        <v>24666.67</v>
+        <v>24333.33</v>
       </c>
     </row>
     <row r="300">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D300" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E300" s="6" t="n">
         <v>750000</v>
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="G300" s="6" t="n">
-        <v>111000000</v>
+        <v>109500000</v>
       </c>
       <c r="H300" s="7" t="n">
-        <v>74000</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="301">
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="D301" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E301" s="6" t="n">
         <v>50000</v>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="G301" s="6" t="n">
-        <v>3700000</v>
+        <v>3650000</v>
       </c>
       <c r="H301" s="7" t="n">
-        <v>2466.67</v>
+        <v>2433.33</v>
       </c>
     </row>
     <row r="302">
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="D310" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E310" s="6" t="n">
         <v>15000</v>
@@ -11104,10 +11104,10 @@
         </is>
       </c>
       <c r="G310" s="6" t="n">
-        <v>2310000</v>
+        <v>2280000</v>
       </c>
       <c r="H310" s="7" t="n">
-        <v>1540</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="311">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="D311" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E311" s="6" t="n">
         <v>250000</v>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="G311" s="6" t="n">
-        <v>38500000</v>
+        <v>38000000</v>
       </c>
       <c r="H311" s="7" t="n">
-        <v>25666.67</v>
+        <v>25333.33</v>
       </c>
     </row>
     <row r="312">
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="D312" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E312" s="6" t="n">
         <v>750000</v>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="G312" s="6" t="n">
-        <v>115500000</v>
+        <v>114000000</v>
       </c>
       <c r="H312" s="7" t="n">
-        <v>77000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="313">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="D313" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E313" s="6" t="n">
         <v>50000</v>
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="G313" s="6" t="n">
-        <v>3850000</v>
+        <v>3800000</v>
       </c>
       <c r="H313" s="7" t="n">
-        <v>2566.67</v>
+        <v>2533.33</v>
       </c>
     </row>
     <row r="314">
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="D322" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E322" s="6" t="n">
         <v>15000</v>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="G322" s="6" t="n">
-        <v>2340000</v>
+        <v>2310000</v>
       </c>
       <c r="H322" s="7" t="n">
-        <v>1560</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="323">
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="D323" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E323" s="6" t="n">
         <v>250000</v>
@@ -11546,10 +11546,10 @@
         </is>
       </c>
       <c r="G323" s="6" t="n">
-        <v>39000000</v>
+        <v>38500000</v>
       </c>
       <c r="H323" s="7" t="n">
-        <v>26000</v>
+        <v>25666.67</v>
       </c>
     </row>
     <row r="324">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="D324" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E324" s="6" t="n">
         <v>750000</v>
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="G324" s="6" t="n">
-        <v>117000000</v>
+        <v>115500000</v>
       </c>
       <c r="H324" s="7" t="n">
-        <v>78000</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="325">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="D325" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E325" s="6" t="n">
         <v>50000</v>
@@ -11614,10 +11614,10 @@
         </is>
       </c>
       <c r="G325" s="6" t="n">
-        <v>3900000</v>
+        <v>3850000</v>
       </c>
       <c r="H325" s="7" t="n">
-        <v>2600</v>
+        <v>2566.67</v>
       </c>
     </row>
     <row r="326">
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="D334" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E334" s="6" t="n">
         <v>15000</v>
@@ -11920,10 +11920,10 @@
         </is>
       </c>
       <c r="G334" s="6" t="n">
-        <v>2370000</v>
+        <v>2340000</v>
       </c>
       <c r="H334" s="7" t="n">
-        <v>1580</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="335">
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="D335" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E335" s="6" t="n">
         <v>250000</v>
@@ -11954,10 +11954,10 @@
         </is>
       </c>
       <c r="G335" s="6" t="n">
-        <v>39500000</v>
+        <v>39000000</v>
       </c>
       <c r="H335" s="7" t="n">
-        <v>26333.33</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="336">
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="D336" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E336" s="6" t="n">
         <v>750000</v>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="G336" s="6" t="n">
-        <v>118500000</v>
+        <v>117000000</v>
       </c>
       <c r="H336" s="7" t="n">
-        <v>79000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="337">
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="D337" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E337" s="6" t="n">
         <v>50000</v>
@@ -12022,10 +12022,10 @@
         </is>
       </c>
       <c r="G337" s="6" t="n">
-        <v>3950000</v>
+        <v>3900000</v>
       </c>
       <c r="H337" s="7" t="n">
-        <v>2633.33</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="338">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="D346" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E346" s="6" t="n">
         <v>15000</v>
@@ -12328,10 +12328,10 @@
         </is>
       </c>
       <c r="G346" s="6" t="n">
-        <v>2400000</v>
+        <v>2370000</v>
       </c>
       <c r="H346" s="7" t="n">
-        <v>1600</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="347">
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="D347" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E347" s="6" t="n">
         <v>250000</v>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="G347" s="6" t="n">
-        <v>40000000</v>
+        <v>39500000</v>
       </c>
       <c r="H347" s="7" t="n">
-        <v>26666.67</v>
+        <v>26333.33</v>
       </c>
     </row>
     <row r="348">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="D348" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E348" s="6" t="n">
         <v>750000</v>
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="G348" s="6" t="n">
-        <v>120000000</v>
+        <v>118500000</v>
       </c>
       <c r="H348" s="7" t="n">
-        <v>80000</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="349">
@@ -12419,7 +12419,7 @@
         </is>
       </c>
       <c r="D349" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E349" s="6" t="n">
         <v>50000</v>
@@ -12430,10 +12430,10 @@
         </is>
       </c>
       <c r="G349" s="6" t="n">
-        <v>4000000</v>
+        <v>3950000</v>
       </c>
       <c r="H349" s="7" t="n">
-        <v>2666.67</v>
+        <v>2633.33</v>
       </c>
     </row>
     <row r="350">
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="D358" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E358" s="6" t="n">
         <v>15000</v>
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="G358" s="6" t="n">
-        <v>2460000</v>
+        <v>2430000</v>
       </c>
       <c r="H358" s="7" t="n">
-        <v>1640</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="359">
@@ -12759,7 +12759,7 @@
         </is>
       </c>
       <c r="D359" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E359" s="6" t="n">
         <v>250000</v>
@@ -12770,10 +12770,10 @@
         </is>
       </c>
       <c r="G359" s="6" t="n">
-        <v>41000000</v>
+        <v>40500000</v>
       </c>
       <c r="H359" s="7" t="n">
-        <v>27333.33</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="360">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="D360" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E360" s="6" t="n">
         <v>750000</v>
@@ -12804,10 +12804,10 @@
         </is>
       </c>
       <c r="G360" s="6" t="n">
-        <v>123000000</v>
+        <v>121500000</v>
       </c>
       <c r="H360" s="7" t="n">
-        <v>82000</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="361">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="D361" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E361" s="6" t="n">
         <v>50000</v>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="G361" s="6" t="n">
-        <v>4100000</v>
+        <v>4050000</v>
       </c>
       <c r="H361" s="7" t="n">
-        <v>2733.33</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="362">
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="D370" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E370" s="6" t="n">
         <v>15000</v>
@@ -13144,10 +13144,10 @@
         </is>
       </c>
       <c r="G370" s="6" t="n">
-        <v>2460000</v>
+        <v>2430000</v>
       </c>
       <c r="H370" s="7" t="n">
-        <v>1640</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="371">
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="D371" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E371" s="6" t="n">
         <v>250000</v>
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="G371" s="6" t="n">
-        <v>41000000</v>
+        <v>40500000</v>
       </c>
       <c r="H371" s="7" t="n">
-        <v>27333.33</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="372">
@@ -13201,7 +13201,7 @@
         </is>
       </c>
       <c r="D372" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E372" s="6" t="n">
         <v>750000</v>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="G372" s="6" t="n">
-        <v>123000000</v>
+        <v>121500000</v>
       </c>
       <c r="H372" s="7" t="n">
-        <v>82000</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="373">
@@ -13235,7 +13235,7 @@
         </is>
       </c>
       <c r="D373" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E373" s="6" t="n">
         <v>50000</v>
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="G373" s="6" t="n">
-        <v>4100000</v>
+        <v>4050000</v>
       </c>
       <c r="H373" s="7" t="n">
-        <v>2733.33</v>
+        <v>2700</v>
       </c>
     </row>
   </sheetData>
@@ -13608,13 +13608,13 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>87360000</v>
+        <v>85280000</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>58240</v>
+        <v>56853.34</v>
       </c>
     </row>
     <row r="17">
@@ -13671,13 +13671,13 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>91520000</v>
+        <v>89440000</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>61013.34</v>
+        <v>59626.66</v>
       </c>
     </row>
     <row r="20">
@@ -13734,13 +13734,13 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>97760000</v>
+        <v>95680000</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>65173.34</v>
+        <v>63786.66</v>
       </c>
     </row>
     <row r="23">
@@ -13797,13 +13797,13 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>97760000</v>
+        <v>95680000</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>65173.34</v>
+        <v>63786.66</v>
       </c>
     </row>
     <row r="26">
@@ -13860,13 +13860,13 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>99840000</v>
+        <v>97760000</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>66560</v>
+        <v>65173.34</v>
       </c>
     </row>
     <row r="29">
@@ -13923,13 +13923,13 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>104000000</v>
+        <v>101920000</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>69333.34</v>
+        <v>67946.66</v>
       </c>
     </row>
     <row r="32">
@@ -13986,13 +13986,13 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>108160000</v>
+        <v>106080000</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>72106.66</v>
+        <v>70720</v>
       </c>
     </row>
     <row r="35">
@@ -14049,13 +14049,13 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>114400000</v>
+        <v>112320000</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>76266.66</v>
+        <v>74880</v>
       </c>
     </row>
     <row r="38">
@@ -14112,13 +14112,13 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>114400000</v>
+        <v>112320000</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>76266.66</v>
+        <v>74880</v>
       </c>
     </row>
     <row r="41">
@@ -14175,13 +14175,13 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>122720000</v>
+        <v>120640000</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>81813.34</v>
+        <v>80426.66</v>
       </c>
     </row>
     <row r="44">
@@ -14238,13 +14238,13 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>122720000</v>
+        <v>120640000</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>81813.34</v>
+        <v>80426.66</v>
       </c>
     </row>
     <row r="47">
@@ -14301,13 +14301,13 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>120640000</v>
+        <v>118560000</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>80426.66</v>
+        <v>79040</v>
       </c>
     </row>
     <row r="50">
@@ -14364,13 +14364,13 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>126880000</v>
+        <v>124800000</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>84586.66</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="53">
@@ -14427,13 +14427,13 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>131040000</v>
+        <v>128960000</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>87360</v>
+        <v>85973.34</v>
       </c>
     </row>
     <row r="56">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>131040000</v>
+        <v>128960000</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>87360</v>
+        <v>85973.34</v>
       </c>
     </row>
     <row r="59">
@@ -14553,13 +14553,13 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>131040000</v>
+        <v>128960000</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>87360</v>
+        <v>85973.34</v>
       </c>
     </row>
     <row r="62">
@@ -14616,13 +14616,13 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>143520000</v>
+        <v>141440000</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>95680</v>
+        <v>94293.34</v>
       </c>
     </row>
     <row r="65">
@@ -14679,13 +14679,13 @@
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>143520000</v>
+        <v>141440000</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>95680</v>
+        <v>94293.34</v>
       </c>
     </row>
     <row r="68">
@@ -14742,13 +14742,13 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>147680000</v>
+        <v>145600000</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>98453.34</v>
+        <v>97066.66</v>
       </c>
     </row>
     <row r="71">
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>149760000</v>
+        <v>147680000</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>99840</v>
+        <v>98453.34</v>
       </c>
     </row>
     <row r="74">
@@ -14868,13 +14868,13 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>153920000</v>
+        <v>151840000</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>102613.34</v>
+        <v>101226.66</v>
       </c>
     </row>
     <row r="77">
@@ -14931,13 +14931,13 @@
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>160160000</v>
+        <v>158080000</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>106773.34</v>
+        <v>105386.66</v>
       </c>
     </row>
     <row r="80">
@@ -14994,13 +14994,13 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>162240000</v>
+        <v>160160000</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>108160</v>
+        <v>106773.34</v>
       </c>
     </row>
     <row r="83">
@@ -15057,13 +15057,13 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>164320000</v>
+        <v>162240000</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>109546.66</v>
+        <v>108160</v>
       </c>
     </row>
     <row r="86">
@@ -15120,13 +15120,13 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>166400000</v>
+        <v>164320000</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>110933.34</v>
+        <v>109546.66</v>
       </c>
     </row>
     <row r="89">
@@ -15183,13 +15183,13 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>170560000</v>
+        <v>168480000</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>113706.66</v>
+        <v>112320</v>
       </c>
     </row>
     <row r="92">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>170560000</v>
+        <v>168480000</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>113706.66</v>
+        <v>112320</v>
       </c>
     </row>
   </sheetData>

--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:10:26.191025+00:00</t>
+          <t>2026-09-01T00:38:12.797681+00:00</t>
         </is>
       </c>
     </row>

--- a/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:38:12.797681+00:00</t>
+          <t>2026-09-01T01:12:21.685661+00:00</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
         <v>6780000</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>4520</v>
+        <v>22090.45</v>
       </c>
     </row>
     <row r="3">
@@ -669,7 +669,7 @@
         <v>113000000</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>75333.33</v>
+        <v>368174.12</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +703,7 @@
         <v>339000000</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>226000</v>
+        <v>1104522.35</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>11300000</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>7533.33</v>
+        <v>36817.41</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         <v>1200000</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>800</v>
+        <v>3909.81</v>
       </c>
     </row>
     <row r="7">
@@ -805,7 +805,7 @@
         <v>20000000</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>13333.33</v>
+        <v>65163.56</v>
       </c>
     </row>
     <row r="8">
@@ -839,7 +839,7 @@
         <v>60000000</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>40000</v>
+        <v>195490.68</v>
       </c>
     </row>
     <row r="9">
@@ -873,7 +873,7 @@
         <v>2000000</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1333.33</v>
+        <v>6516.36</v>
       </c>
     </row>
     <row r="10">
@@ -907,7 +907,7 @@
         <v>510000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>340</v>
+        <v>1661.67</v>
       </c>
     </row>
     <row r="11">
@@ -941,7 +941,7 @@
         <v>8500000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5666.67</v>
+        <v>27694.51</v>
       </c>
     </row>
     <row r="12">
@@ -975,7 +975,7 @@
         <v>25500000</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>17000</v>
+        <v>83083.53999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1009,7 +1009,7 @@
         <v>850000</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>566.67</v>
+        <v>2769.45</v>
       </c>
     </row>
     <row r="14">
@@ -1043,7 +1043,7 @@
         <v>9510000</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>6340</v>
+        <v>30985.27</v>
       </c>
     </row>
     <row r="15">
@@ -1077,7 +1077,7 @@
         <v>158500000</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>105666.67</v>
+        <v>516421.22</v>
       </c>
     </row>
     <row r="16">
@@ -1111,7 +1111,7 @@
         <v>475500000</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>317000</v>
+        <v>1549263.65</v>
       </c>
     </row>
     <row r="17">
@@ -1145,7 +1145,7 @@
         <v>15850000</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>10566.67</v>
+        <v>51642.12</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>2130000</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1420</v>
+        <v>6939.92</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
         <v>35500000</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>23666.67</v>
+        <v>115665.32</v>
       </c>
     </row>
     <row r="20">
@@ -1247,7 +1247,7 @@
         <v>106500000</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>71000</v>
+        <v>346995.96</v>
       </c>
     </row>
     <row r="21">
@@ -1281,7 +1281,7 @@
         <v>3550000</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>2366.67</v>
+        <v>11566.53</v>
       </c>
     </row>
     <row r="22">
@@ -1315,7 +1315,7 @@
         <v>1020000</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>680</v>
+        <v>3323.34</v>
       </c>
     </row>
     <row r="23">
@@ -1349,7 +1349,7 @@
         <v>17000000</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>11333.33</v>
+        <v>55389.03</v>
       </c>
     </row>
     <row r="24">
@@ -1383,7 +1383,7 @@
         <v>51000000</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>34000</v>
+        <v>166167.08</v>
       </c>
     </row>
     <row r="25">
@@ -1417,7 +1417,7 @@
         <v>1700000</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1133.33</v>
+        <v>5538.9</v>
       </c>
     </row>
     <row r="26">
@@ -1451,7 +1451,7 @@
         <v>10440000</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>6960</v>
+        <v>34015.38</v>
       </c>
     </row>
     <row r="27">
@@ -1485,7 +1485,7 @@
         <v>174000000</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>116000</v>
+        <v>566922.98</v>
       </c>
     </row>
     <row r="28">
@@ -1519,7 +1519,7 @@
         <v>522000000</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>348000</v>
+        <v>1700768.93</v>
       </c>
     </row>
     <row r="29">
@@ -1553,7 +1553,7 @@
         <v>17400000</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>11600</v>
+        <v>56692.3</v>
       </c>
     </row>
     <row r="30">
@@ -1587,7 +1587,7 @@
         <v>2520000</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>1680</v>
+        <v>8210.610000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1621,7 +1621,7 @@
         <v>42000000</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>28000</v>
+        <v>136843.48</v>
       </c>
     </row>
     <row r="32">
@@ -1655,7 +1655,7 @@
         <v>126000000</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>84000</v>
+        <v>410530.43</v>
       </c>
     </row>
     <row r="33">
@@ -1689,7 +1689,7 @@
         <v>4200000</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>2800</v>
+        <v>13684.35</v>
       </c>
     </row>
     <row r="34">
@@ -1723,7 +1723,7 @@
         <v>1170000</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>780</v>
+        <v>3812.07</v>
       </c>
     </row>
     <row r="35">
@@ -1757,7 +1757,7 @@
         <v>19500000</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>13000</v>
+        <v>63534.47</v>
       </c>
     </row>
     <row r="36">
@@ -1791,7 +1791,7 @@
         <v>58500000</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>39000</v>
+        <v>190603.41</v>
       </c>
     </row>
     <row r="37">
@@ -1825,7 +1825,7 @@
         <v>1950000</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>1300</v>
+        <v>6353.45</v>
       </c>
     </row>
     <row r="38">
@@ -1859,7 +1859,7 @@
         <v>10620000</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>7080</v>
+        <v>34601.85</v>
       </c>
     </row>
     <row r="39">
@@ -1893,7 +1893,7 @@
         <v>177000000</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>118000</v>
+        <v>576697.51</v>
       </c>
     </row>
     <row r="40">
@@ -1927,7 +1927,7 @@
         <v>531000000</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>354000</v>
+        <v>1730092.53</v>
       </c>
     </row>
     <row r="41">
@@ -1961,7 +1961,7 @@
         <v>17700000</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>11800</v>
+        <v>57669.75</v>
       </c>
     </row>
     <row r="42">
@@ -1995,7 +1995,7 @@
         <v>2550000</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>1700</v>
+        <v>8308.35</v>
       </c>
     </row>
     <row r="43">
@@ -2029,7 +2029,7 @@
         <v>42500000</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>28333.33</v>
+        <v>138472.57</v>
       </c>
     </row>
     <row r="44">
@@ -2063,7 +2063,7 @@
         <v>127500000</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>85000</v>
+        <v>415417.7</v>
       </c>
     </row>
     <row r="45">
@@ -2097,7 +2097,7 @@
         <v>4250000</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>2833.33</v>
+        <v>13847.26</v>
       </c>
     </row>
     <row r="46">
@@ -2131,7 +2131,7 @@
         <v>1230000</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>820</v>
+        <v>4007.56</v>
       </c>
     </row>
     <row r="47">
@@ -2165,7 +2165,7 @@
         <v>20500000</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>13666.67</v>
+        <v>66792.64999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2199,7 +2199,7 @@
         <v>61500000</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>41000</v>
+        <v>200377.95</v>
       </c>
     </row>
     <row r="49">
@@ -2233,7 +2233,7 @@
         <v>2050000</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>1366.67</v>
+        <v>6679.26</v>
       </c>
     </row>
     <row r="50">
@@ -2267,7 +2267,7 @@
         <v>10830000</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>7220</v>
+        <v>30183.11</v>
       </c>
     </row>
     <row r="51">
@@ -2301,7 +2301,7 @@
         <v>180500000</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>120333.33</v>
+        <v>503051.75</v>
       </c>
     </row>
     <row r="52">
@@ -2335,7 +2335,7 @@
         <v>541500000</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>361000</v>
+        <v>1509155.26</v>
       </c>
     </row>
     <row r="53">
@@ -2369,7 +2369,7 @@
         <v>18050000</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>12033.33</v>
+        <v>50305.18</v>
       </c>
     </row>
     <row r="54">
@@ -2403,7 +2403,7 @@
         <v>2580000</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>1720</v>
+        <v>7190.44</v>
       </c>
     </row>
     <row r="55">
@@ -2437,7 +2437,7 @@
         <v>43000000</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>28666.67</v>
+        <v>119840.58</v>
       </c>
     </row>
     <row r="56">
@@ -2471,7 +2471,7 @@
         <v>129000000</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>86000</v>
+        <v>359521.75</v>
       </c>
     </row>
     <row r="57">
@@ -2505,7 +2505,7 @@
         <v>4300000</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>2866.67</v>
+        <v>11984.06</v>
       </c>
     </row>
     <row r="58">
@@ -2539,7 +2539,7 @@
         <v>1230000</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>820</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="59">
@@ -2573,7 +2573,7 @@
         <v>20500000</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>13666.67</v>
+        <v>57133.3</v>
       </c>
     </row>
     <row r="60">
@@ -2607,7 +2607,7 @@
         <v>61500000</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>41000</v>
+        <v>171399.91</v>
       </c>
     </row>
     <row r="61">
@@ -2641,7 +2641,7 @@
         <v>2050000</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>1366.67</v>
+        <v>5713.33</v>
       </c>
     </row>
     <row r="62">
@@ -2675,7 +2675,7 @@
         <v>11580000</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>7720</v>
+        <v>32273.35</v>
       </c>
     </row>
     <row r="63">
@@ -2709,7 +2709,7 @@
         <v>193000000</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>128666.67</v>
+        <v>537889.13</v>
       </c>
     </row>
     <row r="64">
@@ -2743,7 +2743,7 @@
         <v>579000000</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>386000</v>
+        <v>1613667.4</v>
       </c>
     </row>
     <row r="65">
@@ -2777,7 +2777,7 @@
         <v>19300000</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>12866.67</v>
+        <v>53788.91</v>
       </c>
     </row>
     <row r="66">
@@ -2811,7 +2811,7 @@
         <v>2790000</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>1860</v>
+        <v>7775.7</v>
       </c>
     </row>
     <row r="67">
@@ -2845,7 +2845,7 @@
         <v>46500000</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>31000</v>
+        <v>129595.05</v>
       </c>
     </row>
     <row r="68">
@@ -2879,7 +2879,7 @@
         <v>139500000</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>93000</v>
+        <v>388785.15</v>
       </c>
     </row>
     <row r="69">
@@ -2913,7 +2913,7 @@
         <v>4650000</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>3100</v>
+        <v>12959.51</v>
       </c>
     </row>
     <row r="70">
@@ -2947,7 +2947,7 @@
         <v>1290000</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>860</v>
+        <v>3595.22</v>
       </c>
     </row>
     <row r="71">
@@ -2981,7 +2981,7 @@
         <v>21500000</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>14333.33</v>
+        <v>59920.29</v>
       </c>
     </row>
     <row r="72">
@@ -3015,7 +3015,7 @@
         <v>64500000</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>43000</v>
+        <v>179760.88</v>
       </c>
     </row>
     <row r="73">
@@ -3049,7 +3049,7 @@
         <v>2150000</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>1433.33</v>
+        <v>5992.03</v>
       </c>
     </row>
     <row r="74">
@@ -3083,7 +3083,7 @@
         <v>12240000</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>8160</v>
+        <v>34112.76</v>
       </c>
     </row>
     <row r="75">
@@ -3117,7 +3117,7 @@
         <v>204000000</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>136000</v>
+        <v>568546.03</v>
       </c>
     </row>
     <row r="76">
@@ -3151,7 +3151,7 @@
         <v>612000000</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>408000</v>
+        <v>1705638.08</v>
       </c>
     </row>
     <row r="77">
@@ -3185,7 +3185,7 @@
         <v>20400000</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>13600</v>
+        <v>56854.6</v>
       </c>
     </row>
     <row r="78">
@@ -3219,7 +3219,7 @@
         <v>2850000</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>1900</v>
+        <v>7942.92</v>
       </c>
     </row>
     <row r="79">
@@ -3253,7 +3253,7 @@
         <v>47500000</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>31666.67</v>
+        <v>132382.04</v>
       </c>
     </row>
     <row r="80">
@@ -3287,7 +3287,7 @@
         <v>142500000</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>95000</v>
+        <v>397146.12</v>
       </c>
     </row>
     <row r="81">
@@ -3321,7 +3321,7 @@
         <v>4750000</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>3166.67</v>
+        <v>13238.2</v>
       </c>
     </row>
     <row r="82">
@@ -3355,7 +3355,7 @@
         <v>1380000</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>920</v>
+        <v>3846.05</v>
       </c>
     </row>
     <row r="83">
@@ -3389,7 +3389,7 @@
         <v>23000000</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>15333.33</v>
+        <v>64100.78</v>
       </c>
     </row>
     <row r="84">
@@ -3423,7 +3423,7 @@
         <v>69000000</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>46000</v>
+        <v>192302.33</v>
       </c>
     </row>
     <row r="85">
@@ -3457,7 +3457,7 @@
         <v>2300000</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>1533.33</v>
+        <v>6410.08</v>
       </c>
     </row>
     <row r="86">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>15000</v>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="G86" s="6" t="n">
-        <v>12600000</v>
+        <v>12570000</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>8400</v>
+        <v>35032.47</v>
       </c>
     </row>
     <row r="87">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>250000</v>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>210000000</v>
+        <v>209500000</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>140000</v>
+        <v>583874.47</v>
       </c>
     </row>
     <row r="88">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>750000</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>630000000</v>
+        <v>628500000</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>420000</v>
+        <v>1751623.42</v>
       </c>
     </row>
     <row r="89">
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>50000</v>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>21000000</v>
+        <v>20950000</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>14000</v>
+        <v>58387.45</v>
       </c>
     </row>
     <row r="90">
@@ -3627,7 +3627,7 @@
         <v>2940000</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>1960</v>
+        <v>8193.75</v>
       </c>
     </row>
     <row r="91">
@@ -3661,7 +3661,7 @@
         <v>49000000</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>32666.67</v>
+        <v>136562.53</v>
       </c>
     </row>
     <row r="92">
@@ -3695,7 +3695,7 @@
         <v>147000000</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>98000</v>
+        <v>409687.58</v>
       </c>
     </row>
     <row r="93">
@@ -3729,7 +3729,7 @@
         <v>4900000</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>3266.67</v>
+        <v>13656.25</v>
       </c>
     </row>
     <row r="94">
@@ -3763,7 +3763,7 @@
         <v>1380000</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>920</v>
+        <v>3846.05</v>
       </c>
     </row>
     <row r="95">
@@ -3797,7 +3797,7 @@
         <v>23000000</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>15333.33</v>
+        <v>64100.78</v>
       </c>
     </row>
     <row r="96">
@@ -3831,7 +3831,7 @@
         <v>69000000</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>46000</v>
+        <v>192302.33</v>
       </c>
     </row>
     <row r="97">
@@ -3865,7 +3865,7 @@
         <v>2300000</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>1533.33</v>
+        <v>6410.08</v>
       </c>
     </row>
     <row r="98">
@@ -3899,7 +3899,7 @@
         <v>12780000</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>8520</v>
+        <v>31858.41</v>
       </c>
     </row>
     <row r="99">
@@ -3933,7 +3933,7 @@
         <v>213000000</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>142000</v>
+        <v>530973.45</v>
       </c>
     </row>
     <row r="100">
@@ -3967,7 +3967,7 @@
         <v>639000000</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>426000</v>
+        <v>1592920.35</v>
       </c>
     </row>
     <row r="101">
@@ -4001,7 +4001,7 @@
         <v>21300000</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>14200</v>
+        <v>53097.35</v>
       </c>
     </row>
     <row r="102">
@@ -4035,7 +4035,7 @@
         <v>3030000</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>2020</v>
+        <v>7553.28</v>
       </c>
     </row>
     <row r="103">
@@ -4069,7 +4069,7 @@
         <v>50500000</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>33666.67</v>
+        <v>125888.07</v>
       </c>
     </row>
     <row r="104">
@@ -4103,7 +4103,7 @@
         <v>151500000</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>101000</v>
+        <v>377664.22</v>
       </c>
     </row>
     <row r="105">
@@ -4137,7 +4137,7 @@
         <v>5050000</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>3366.67</v>
+        <v>12588.81</v>
       </c>
     </row>
     <row r="106">
@@ -4171,7 +4171,7 @@
         <v>1410000</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>940</v>
+        <v>3514.89</v>
       </c>
     </row>
     <row r="107">
@@ -4205,7 +4205,7 @@
         <v>23500000</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>15666.67</v>
+        <v>58581.58</v>
       </c>
     </row>
     <row r="108">
@@ -4239,7 +4239,7 @@
         <v>70500000</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>47000</v>
+        <v>175744.73</v>
       </c>
     </row>
     <row r="109">
@@ -4273,7 +4273,7 @@
         <v>2350000</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>1566.67</v>
+        <v>5858.16</v>
       </c>
     </row>
     <row r="110">
@@ -4307,7 +4307,7 @@
         <v>13050000</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>8700</v>
+        <v>32531.47</v>
       </c>
     </row>
     <row r="111">
@@ -4341,7 +4341,7 @@
         <v>217500000</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>145000</v>
+        <v>542191.2</v>
       </c>
     </row>
     <row r="112">
@@ -4375,7 +4375,7 @@
         <v>652500000</v>
       </c>
       <c r="H112" s="7" t="n">
-        <v>435000</v>
+        <v>1626573.6</v>
       </c>
     </row>
     <row r="113">
@@ -4409,7 +4409,7 @@
         <v>21750000</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>14500</v>
+        <v>54219.12</v>
       </c>
     </row>
     <row r="114">
@@ -4443,7 +4443,7 @@
         <v>3060000</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>2040</v>
+        <v>7628.07</v>
       </c>
     </row>
     <row r="115">
@@ -4477,7 +4477,7 @@
         <v>51000000</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>34000</v>
+        <v>127134.49</v>
       </c>
     </row>
     <row r="116">
@@ -4511,7 +4511,7 @@
         <v>153000000</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>102000</v>
+        <v>381403.47</v>
       </c>
     </row>
     <row r="117">
@@ -4545,7 +4545,7 @@
         <v>5100000</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>3400</v>
+        <v>12713.45</v>
       </c>
     </row>
     <row r="118">
@@ -4579,7 +4579,7 @@
         <v>1470000</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>980</v>
+        <v>3664.46</v>
       </c>
     </row>
     <row r="119">
@@ -4613,7 +4613,7 @@
         <v>24500000</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>16333.33</v>
+        <v>61074.41</v>
       </c>
     </row>
     <row r="120">
@@ -4647,7 +4647,7 @@
         <v>73500000</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>49000</v>
+        <v>183223.23</v>
       </c>
     </row>
     <row r="121">
@@ -4681,7 +4681,7 @@
         <v>2450000</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>1633.33</v>
+        <v>6107.44</v>
       </c>
     </row>
     <row r="122">
@@ -4715,7 +4715,7 @@
         <v>13140000</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>8760</v>
+        <v>32755.83</v>
       </c>
     </row>
     <row r="123">
@@ -4749,7 +4749,7 @@
         <v>219000000</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>146000</v>
+        <v>545930.45</v>
       </c>
     </row>
     <row r="124">
@@ -4783,7 +4783,7 @@
         <v>657000000</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>438000</v>
+        <v>1637791.35</v>
       </c>
     </row>
     <row r="125">
@@ -4817,7 +4817,7 @@
         <v>21900000</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>14600</v>
+        <v>54593.04</v>
       </c>
     </row>
     <row r="126">
@@ -4851,7 +4851,7 @@
         <v>3150000</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>2100</v>
+        <v>7852.42</v>
       </c>
     </row>
     <row r="127">
@@ -4885,7 +4885,7 @@
         <v>52500000</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>35000</v>
+        <v>130873.74</v>
       </c>
     </row>
     <row r="128">
@@ -4919,7 +4919,7 @@
         <v>157500000</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>105000</v>
+        <v>392621.21</v>
       </c>
     </row>
     <row r="129">
@@ -4953,7 +4953,7 @@
         <v>5250000</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>3500</v>
+        <v>13087.37</v>
       </c>
     </row>
     <row r="130">
@@ -4987,7 +4987,7 @@
         <v>1530000</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>1020</v>
+        <v>3814.03</v>
       </c>
     </row>
     <row r="131">
@@ -5021,7 +5021,7 @@
         <v>25500000</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>17000</v>
+        <v>63567.24</v>
       </c>
     </row>
     <row r="132">
@@ -5055,7 +5055,7 @@
         <v>76500000</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>51000</v>
+        <v>190701.73</v>
       </c>
     </row>
     <row r="133">
@@ -5089,7 +5089,7 @@
         <v>2550000</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>1700</v>
+        <v>6356.72</v>
       </c>
     </row>
     <row r="134">
@@ -5123,7 +5123,7 @@
         <v>13530000</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>9020</v>
+        <v>33728.03</v>
       </c>
     </row>
     <row r="135">
@@ -5157,7 +5157,7 @@
         <v>225500000</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>150333.33</v>
+        <v>562133.87</v>
       </c>
     </row>
     <row r="136">
@@ -5191,7 +5191,7 @@
         <v>676500000</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>451000</v>
+        <v>1686401.6</v>
       </c>
     </row>
     <row r="137">
@@ -5225,7 +5225,7 @@
         <v>22550000</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>15033.33</v>
+        <v>56213.39</v>
       </c>
     </row>
     <row r="138">
@@ -5259,7 +5259,7 @@
         <v>3150000</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>2100</v>
+        <v>7852.42</v>
       </c>
     </row>
     <row r="139">
@@ -5293,7 +5293,7 @@
         <v>52500000</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>35000</v>
+        <v>130873.74</v>
       </c>
     </row>
     <row r="140">
@@ -5327,7 +5327,7 @@
         <v>157500000</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>105000</v>
+        <v>392621.21</v>
       </c>
     </row>
     <row r="141">
@@ -5361,7 +5361,7 @@
         <v>5250000</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>3500</v>
+        <v>13087.37</v>
       </c>
     </row>
     <row r="142">
@@ -5395,7 +5395,7 @@
         <v>1620000</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>1080</v>
+        <v>4038.39</v>
       </c>
     </row>
     <row r="143">
@@ -5429,7 +5429,7 @@
         <v>27000000</v>
       </c>
       <c r="H143" s="7" t="n">
-        <v>18000</v>
+        <v>67306.49000000001</v>
       </c>
     </row>
     <row r="144">
@@ -5463,7 +5463,7 @@
         <v>81000000</v>
       </c>
       <c r="H144" s="7" t="n">
-        <v>54000</v>
+        <v>201919.48</v>
       </c>
     </row>
     <row r="145">
@@ -5497,7 +5497,7 @@
         <v>2700000</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>1800</v>
+        <v>6730.65</v>
       </c>
     </row>
     <row r="146">
@@ -5531,7 +5531,7 @@
         <v>13710000</v>
       </c>
       <c r="H146" s="7" t="n">
-        <v>9140</v>
+        <v>32184.61</v>
       </c>
     </row>
     <row r="147">
@@ -5565,7 +5565,7 @@
         <v>228500000</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>152333.33</v>
+        <v>536410.16</v>
       </c>
     </row>
     <row r="148">
@@ -5599,7 +5599,7 @@
         <v>685500000</v>
       </c>
       <c r="H148" s="7" t="n">
-        <v>457000</v>
+        <v>1609230.48</v>
       </c>
     </row>
     <row r="149">
@@ -5633,7 +5633,7 @@
         <v>22850000</v>
       </c>
       <c r="H149" s="7" t="n">
-        <v>15233.33</v>
+        <v>53641.02</v>
       </c>
     </row>
     <row r="150">
@@ -5667,7 +5667,7 @@
         <v>3210000</v>
       </c>
       <c r="H150" s="7" t="n">
-        <v>2140</v>
+        <v>7535.57</v>
       </c>
     </row>
     <row r="151">
@@ -5701,7 +5701,7 @@
         <v>53500000</v>
       </c>
       <c r="H151" s="7" t="n">
-        <v>35666.67</v>
+        <v>125592.75</v>
       </c>
     </row>
     <row r="152">
@@ -5735,7 +5735,7 @@
         <v>160500000</v>
       </c>
       <c r="H152" s="7" t="n">
-        <v>107000</v>
+        <v>376778.25</v>
       </c>
     </row>
     <row r="153">
@@ -5769,7 +5769,7 @@
         <v>5350000</v>
       </c>
       <c r="H153" s="7" t="n">
-        <v>3566.67</v>
+        <v>12559.28</v>
       </c>
     </row>
     <row r="154">
@@ -5803,7 +5803,7 @@
         <v>1620000</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>1080</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="155">
@@ -5837,7 +5837,7 @@
         <v>27000000</v>
       </c>
       <c r="H155" s="7" t="n">
-        <v>18000</v>
+        <v>63383.26</v>
       </c>
     </row>
     <row r="156">
@@ -5871,7 +5871,7 @@
         <v>81000000</v>
       </c>
       <c r="H156" s="7" t="n">
-        <v>54000</v>
+        <v>190149.77</v>
       </c>
     </row>
     <row r="157">
@@ -5905,7 +5905,7 @@
         <v>2700000</v>
       </c>
       <c r="H157" s="7" t="n">
-        <v>1800</v>
+        <v>6338.33</v>
       </c>
     </row>
     <row r="158">
@@ -5939,7 +5939,7 @@
         <v>13830000</v>
       </c>
       <c r="H158" s="7" t="n">
-        <v>9220</v>
+        <v>32466.31</v>
       </c>
     </row>
     <row r="159">
@@ -5973,7 +5973,7 @@
         <v>230500000</v>
       </c>
       <c r="H159" s="7" t="n">
-        <v>153666.67</v>
+        <v>541105.22</v>
       </c>
     </row>
     <row r="160">
@@ -6007,7 +6007,7 @@
         <v>691500000</v>
       </c>
       <c r="H160" s="7" t="n">
-        <v>461000</v>
+        <v>1623315.65</v>
       </c>
     </row>
     <row r="161">
@@ -6041,7 +6041,7 @@
         <v>23050000</v>
       </c>
       <c r="H161" s="7" t="n">
-        <v>15366.67</v>
+        <v>54110.52</v>
       </c>
     </row>
     <row r="162">
@@ -6075,7 +6075,7 @@
         <v>3210000</v>
       </c>
       <c r="H162" s="7" t="n">
-        <v>2140</v>
+        <v>7535.57</v>
       </c>
     </row>
     <row r="163">
@@ -6109,7 +6109,7 @@
         <v>53500000</v>
       </c>
       <c r="H163" s="7" t="n">
-        <v>35666.67</v>
+        <v>125592.75</v>
       </c>
     </row>
     <row r="164">
@@ -6143,7 +6143,7 @@
         <v>160500000</v>
       </c>
       <c r="H164" s="7" t="n">
-        <v>107000</v>
+        <v>376778.25</v>
       </c>
     </row>
     <row r="165">
@@ -6177,7 +6177,7 @@
         <v>5350000</v>
       </c>
       <c r="H165" s="7" t="n">
-        <v>3566.67</v>
+        <v>12559.28</v>
       </c>
     </row>
     <row r="166">
@@ -6211,7 +6211,7 @@
         <v>1740000</v>
       </c>
       <c r="H166" s="7" t="n">
-        <v>1160</v>
+        <v>4084.7</v>
       </c>
     </row>
     <row r="167">
@@ -6245,7 +6245,7 @@
         <v>29000000</v>
       </c>
       <c r="H167" s="7" t="n">
-        <v>19333.33</v>
+        <v>68078.31</v>
       </c>
     </row>
     <row r="168">
@@ -6279,7 +6279,7 @@
         <v>87000000</v>
       </c>
       <c r="H168" s="7" t="n">
-        <v>58000</v>
+        <v>204234.94</v>
       </c>
     </row>
     <row r="169">
@@ -6313,7 +6313,7 @@
         <v>2900000</v>
       </c>
       <c r="H169" s="7" t="n">
-        <v>1933.33</v>
+        <v>6807.83</v>
       </c>
     </row>
     <row r="170">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E170" s="6" t="n">
         <v>15000</v>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="G170" s="6" t="n">
-        <v>14160000</v>
+        <v>14130000</v>
       </c>
       <c r="H170" s="7" t="n">
-        <v>9440</v>
+        <v>33170.57</v>
       </c>
     </row>
     <row r="171">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E171" s="6" t="n">
         <v>250000</v>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="G171" s="6" t="n">
-        <v>236000000</v>
+        <v>235500000</v>
       </c>
       <c r="H171" s="7" t="n">
-        <v>157333.33</v>
+        <v>552842.86</v>
       </c>
     </row>
     <row r="172">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="D172" s="6" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E172" s="6" t="n">
         <v>750000</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="G172" s="6" t="n">
-        <v>708000000</v>
+        <v>706500000</v>
       </c>
       <c r="H172" s="7" t="n">
-        <v>472000</v>
+        <v>1658528.57</v>
       </c>
     </row>
     <row r="173">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="D173" s="6" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E173" s="6" t="n">
         <v>50000</v>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="G173" s="6" t="n">
-        <v>23600000</v>
+        <v>23550000</v>
       </c>
       <c r="H173" s="7" t="n">
-        <v>15733.33</v>
+        <v>55284.29</v>
       </c>
     </row>
     <row r="174">
@@ -6483,7 +6483,7 @@
         <v>3270000</v>
       </c>
       <c r="H174" s="7" t="n">
-        <v>2180</v>
+        <v>7676.42</v>
       </c>
     </row>
     <row r="175">
@@ -6517,7 +6517,7 @@
         <v>54500000</v>
       </c>
       <c r="H175" s="7" t="n">
-        <v>36333.33</v>
+        <v>127940.28</v>
       </c>
     </row>
     <row r="176">
@@ -6551,7 +6551,7 @@
         <v>163500000</v>
       </c>
       <c r="H176" s="7" t="n">
-        <v>109000</v>
+        <v>383820.84</v>
       </c>
     </row>
     <row r="177">
@@ -6585,7 +6585,7 @@
         <v>5450000</v>
       </c>
       <c r="H177" s="7" t="n">
-        <v>3633.33</v>
+        <v>12794.03</v>
       </c>
     </row>
     <row r="178">
@@ -6619,7 +6619,7 @@
         <v>1740000</v>
       </c>
       <c r="H178" s="7" t="n">
-        <v>1160</v>
+        <v>4084.7</v>
       </c>
     </row>
     <row r="179">
@@ -6653,7 +6653,7 @@
         <v>29000000</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>19333.33</v>
+        <v>68078.31</v>
       </c>
     </row>
     <row r="180">
@@ -6687,7 +6687,7 @@
         <v>87000000</v>
       </c>
       <c r="H180" s="7" t="n">
-        <v>58000</v>
+        <v>204234.94</v>
       </c>
     </row>
     <row r="181">
@@ -6721,7 +6721,7 @@
         <v>2900000</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>1933.33</v>
+        <v>6807.83</v>
       </c>
     </row>
     <row r="182">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="D182" s="6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E182" s="6" t="n">
         <v>15000</v>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="G182" s="6" t="n">
-        <v>14340000</v>
+        <v>14310000</v>
       </c>
       <c r="H182" s="7" t="n">
-        <v>9560</v>
+        <v>33593.13</v>
       </c>
     </row>
     <row r="183">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E183" s="6" t="n">
         <v>250000</v>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="G183" s="6" t="n">
-        <v>239000000</v>
+        <v>238500000</v>
       </c>
       <c r="H183" s="7" t="n">
-        <v>159333.33</v>
+        <v>559885.4399999999</v>
       </c>
     </row>
     <row r="184">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E184" s="6" t="n">
         <v>750000</v>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="G184" s="6" t="n">
-        <v>717000000</v>
+        <v>715500000</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>478000</v>
+        <v>1679656.32</v>
       </c>
     </row>
     <row r="185">
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E185" s="6" t="n">
         <v>50000</v>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="G185" s="6" t="n">
-        <v>23900000</v>
+        <v>23850000</v>
       </c>
       <c r="H185" s="7" t="n">
-        <v>15933.33</v>
+        <v>55988.54</v>
       </c>
     </row>
     <row r="186">
@@ -6891,7 +6891,7 @@
         <v>3330000</v>
       </c>
       <c r="H186" s="7" t="n">
-        <v>2220</v>
+        <v>7817.27</v>
       </c>
     </row>
     <row r="187">
@@ -6925,7 +6925,7 @@
         <v>55500000</v>
       </c>
       <c r="H187" s="7" t="n">
-        <v>37000</v>
+        <v>130287.81</v>
       </c>
     </row>
     <row r="188">
@@ -6959,7 +6959,7 @@
         <v>166500000</v>
       </c>
       <c r="H188" s="7" t="n">
-        <v>111000</v>
+        <v>390863.42</v>
       </c>
     </row>
     <row r="189">
@@ -6993,7 +6993,7 @@
         <v>5550000</v>
       </c>
       <c r="H189" s="7" t="n">
-        <v>3700</v>
+        <v>13028.78</v>
       </c>
     </row>
     <row r="190">
@@ -7027,7 +7027,7 @@
         <v>1710000</v>
       </c>
       <c r="H190" s="7" t="n">
-        <v>1140</v>
+        <v>4014.27</v>
       </c>
     </row>
     <row r="191">
@@ -7061,7 +7061,7 @@
         <v>28500000</v>
       </c>
       <c r="H191" s="7" t="n">
-        <v>19000</v>
+        <v>66904.55</v>
       </c>
     </row>
     <row r="192">
@@ -7095,7 +7095,7 @@
         <v>85500000</v>
       </c>
       <c r="H192" s="7" t="n">
-        <v>57000</v>
+        <v>200713.65</v>
       </c>
     </row>
     <row r="193">
@@ -7129,7 +7129,7 @@
         <v>2850000</v>
       </c>
       <c r="H193" s="7" t="n">
-        <v>1900</v>
+        <v>6690.45</v>
       </c>
     </row>
     <row r="194">
@@ -7163,7 +7163,7 @@
         <v>14520000</v>
       </c>
       <c r="H194" s="7" t="n">
-        <v>9680</v>
+        <v>22511.63</v>
       </c>
     </row>
     <row r="195">
@@ -7197,7 +7197,7 @@
         <v>242000000</v>
       </c>
       <c r="H195" s="7" t="n">
-        <v>161333.33</v>
+        <v>375193.8</v>
       </c>
     </row>
     <row r="196">
@@ -7231,7 +7231,7 @@
         <v>726000000</v>
       </c>
       <c r="H196" s="7" t="n">
-        <v>484000</v>
+        <v>1125581.4</v>
       </c>
     </row>
     <row r="197">
@@ -7265,7 +7265,7 @@
         <v>24200000</v>
       </c>
       <c r="H197" s="7" t="n">
-        <v>16133.33</v>
+        <v>37519.38</v>
       </c>
     </row>
     <row r="198">
@@ -7299,7 +7299,7 @@
         <v>3300000</v>
       </c>
       <c r="H198" s="7" t="n">
-        <v>2200</v>
+        <v>5116.28</v>
       </c>
     </row>
     <row r="199">
@@ -7333,7 +7333,7 @@
         <v>55000000</v>
       </c>
       <c r="H199" s="7" t="n">
-        <v>36666.67</v>
+        <v>85271.32000000001</v>
       </c>
     </row>
     <row r="200">
@@ -7367,7 +7367,7 @@
         <v>165000000</v>
       </c>
       <c r="H200" s="7" t="n">
-        <v>110000</v>
+        <v>255813.95</v>
       </c>
     </row>
     <row r="201">
@@ -7401,7 +7401,7 @@
         <v>5500000</v>
       </c>
       <c r="H201" s="7" t="n">
-        <v>3666.67</v>
+        <v>8527.129999999999</v>
       </c>
     </row>
     <row r="202">
@@ -7435,7 +7435,7 @@
         <v>1800000</v>
       </c>
       <c r="H202" s="7" t="n">
-        <v>1200</v>
+        <v>2790.7</v>
       </c>
     </row>
     <row r="203">
@@ -7469,7 +7469,7 @@
         <v>30000000</v>
       </c>
       <c r="H203" s="7" t="n">
-        <v>20000</v>
+        <v>46511.63</v>
       </c>
     </row>
     <row r="204">
@@ -7503,7 +7503,7 @@
         <v>90000000</v>
       </c>
       <c r="H204" s="7" t="n">
-        <v>60000</v>
+        <v>139534.88</v>
       </c>
     </row>
     <row r="205">
@@ -7537,7 +7537,7 @@
         <v>3000000</v>
       </c>
       <c r="H205" s="7" t="n">
-        <v>2000</v>
+        <v>4651.16</v>
       </c>
     </row>
     <row r="206">
@@ -7571,7 +7571,7 @@
         <v>14820000</v>
       </c>
       <c r="H206" s="7" t="n">
-        <v>9880</v>
+        <v>22976.74</v>
       </c>
     </row>
     <row r="207">
@@ -7605,7 +7605,7 @@
         <v>247000000</v>
       </c>
       <c r="H207" s="7" t="n">
-        <v>164666.67</v>
+        <v>382945.74</v>
       </c>
     </row>
     <row r="208">
@@ -7639,7 +7639,7 @@
         <v>741000000</v>
       </c>
       <c r="H208" s="7" t="n">
-        <v>494000</v>
+        <v>1148837.21</v>
       </c>
     </row>
     <row r="209">
@@ -7673,7 +7673,7 @@
         <v>24700000</v>
       </c>
       <c r="H209" s="7" t="n">
-        <v>16466.67</v>
+        <v>38294.57</v>
       </c>
     </row>
     <row r="210">
@@ -7707,7 +7707,7 @@
         <v>3390000</v>
       </c>
       <c r="H210" s="7" t="n">
-        <v>2260</v>
+        <v>5255.81</v>
       </c>
     </row>
     <row r="211">
@@ -7741,7 +7741,7 @@
         <v>56500000</v>
       </c>
       <c r="H211" s="7" t="n">
-        <v>37666.67</v>
+        <v>87596.89999999999</v>
       </c>
     </row>
     <row r="212">
@@ -7775,7 +7775,7 @@
         <v>169500000</v>
       </c>
       <c r="H212" s="7" t="n">
-        <v>113000</v>
+        <v>262790.7</v>
       </c>
     </row>
     <row r="213">
@@ -7809,7 +7809,7 @@
         <v>5650000</v>
       </c>
       <c r="H213" s="7" t="n">
-        <v>3766.67</v>
+        <v>8759.690000000001</v>
       </c>
     </row>
     <row r="214">
@@ -7843,7 +7843,7 @@
         <v>1860000</v>
       </c>
       <c r="H214" s="7" t="n">
-        <v>1240</v>
+        <v>2883.72</v>
       </c>
     </row>
     <row r="215">
@@ -7877,7 +7877,7 @@
         <v>31000000</v>
       </c>
       <c r="H215" s="7" t="n">
-        <v>20666.67</v>
+        <v>48062.02</v>
       </c>
     </row>
     <row r="216">
@@ -7911,7 +7911,7 @@
         <v>93000000</v>
       </c>
       <c r="H216" s="7" t="n">
-        <v>62000</v>
+        <v>144186.05</v>
       </c>
     </row>
     <row r="217">
@@ -7945,7 +7945,7 @@
         <v>3100000</v>
       </c>
       <c r="H217" s="7" t="n">
-        <v>2066.67</v>
+        <v>4806.2</v>
       </c>
     </row>
     <row r="218">
@@ -7979,7 +7979,7 @@
         <v>14790000</v>
       </c>
       <c r="H218" s="7" t="n">
-        <v>9860</v>
+        <v>22930.23</v>
       </c>
     </row>
     <row r="219">
@@ -8013,7 +8013,7 @@
         <v>246500000</v>
       </c>
       <c r="H219" s="7" t="n">
-        <v>164333.33</v>
+        <v>382170.54</v>
       </c>
     </row>
     <row r="220">
@@ -8047,7 +8047,7 @@
         <v>739500000</v>
       </c>
       <c r="H220" s="7" t="n">
-        <v>493000</v>
+        <v>1146511.63</v>
       </c>
     </row>
     <row r="221">
@@ -8081,7 +8081,7 @@
         <v>24650000</v>
       </c>
       <c r="H221" s="7" t="n">
-        <v>16433.33</v>
+        <v>38217.05</v>
       </c>
     </row>
     <row r="222">
@@ -8115,7 +8115,7 @@
         <v>3390000</v>
       </c>
       <c r="H222" s="7" t="n">
-        <v>2260</v>
+        <v>5255.81</v>
       </c>
     </row>
     <row r="223">
@@ -8149,7 +8149,7 @@
         <v>56500000</v>
       </c>
       <c r="H223" s="7" t="n">
-        <v>37666.67</v>
+        <v>87596.89999999999</v>
       </c>
     </row>
     <row r="224">
@@ -8183,7 +8183,7 @@
         <v>169500000</v>
       </c>
       <c r="H224" s="7" t="n">
-        <v>113000</v>
+        <v>262790.7</v>
       </c>
     </row>
     <row r="225">
@@ -8217,7 +8217,7 @@
         <v>5650000</v>
       </c>
       <c r="H225" s="7" t="n">
-        <v>3766.67</v>
+        <v>8759.690000000001</v>
       </c>
     </row>
     <row r="226">
@@ -8251,7 +8251,7 @@
         <v>1860000</v>
       </c>
       <c r="H226" s="7" t="n">
-        <v>1240</v>
+        <v>2883.72</v>
       </c>
     </row>
     <row r="227">
@@ -8285,7 +8285,7 @@
         <v>31000000</v>
       </c>
       <c r="H227" s="7" t="n">
-        <v>20666.67</v>
+        <v>48062.02</v>
       </c>
     </row>
     <row r="228">
@@ -8319,7 +8319,7 @@
         <v>93000000</v>
       </c>
       <c r="H228" s="7" t="n">
-        <v>62000</v>
+        <v>144186.05</v>
       </c>
     </row>
     <row r="229">
@@ -8353,7 +8353,7 @@
         <v>3100000</v>
       </c>
       <c r="H229" s="7" t="n">
-        <v>2066.67</v>
+        <v>4806.2</v>
       </c>
     </row>
     <row r="230">
@@ -8387,7 +8387,7 @@
         <v>14880000</v>
       </c>
       <c r="H230" s="7" t="n">
-        <v>9920</v>
+        <v>23069.77</v>
       </c>
     </row>
     <row r="231">
@@ -8421,7 +8421,7 @@
         <v>248000000</v>
       </c>
       <c r="H231" s="7" t="n">
-        <v>165333.33</v>
+        <v>384496.12</v>
       </c>
     </row>
     <row r="232">
@@ -8455,7 +8455,7 @@
         <v>744000000</v>
       </c>
       <c r="H232" s="7" t="n">
-        <v>496000</v>
+        <v>1153488.37</v>
       </c>
     </row>
     <row r="233">
@@ -8489,7 +8489,7 @@
         <v>24800000</v>
       </c>
       <c r="H233" s="7" t="n">
-        <v>16533.33</v>
+        <v>38449.61</v>
       </c>
     </row>
     <row r="234">
@@ -8523,7 +8523,7 @@
         <v>3390000</v>
       </c>
       <c r="H234" s="7" t="n">
-        <v>2260</v>
+        <v>5255.81</v>
       </c>
     </row>
     <row r="235">
@@ -8557,7 +8557,7 @@
         <v>56500000</v>
       </c>
       <c r="H235" s="7" t="n">
-        <v>37666.67</v>
+        <v>87596.89999999999</v>
       </c>
     </row>
     <row r="236">
@@ -8591,7 +8591,7 @@
         <v>169500000</v>
       </c>
       <c r="H236" s="7" t="n">
-        <v>113000</v>
+        <v>262790.7</v>
       </c>
     </row>
     <row r="237">
@@ -8625,7 +8625,7 @@
         <v>5650000</v>
       </c>
       <c r="H237" s="7" t="n">
-        <v>3766.67</v>
+        <v>8759.690000000001</v>
       </c>
     </row>
     <row r="238">
@@ -8659,7 +8659,7 @@
         <v>1860000</v>
       </c>
       <c r="H238" s="7" t="n">
-        <v>1240</v>
+        <v>2883.72</v>
       </c>
     </row>
     <row r="239">
@@ -8693,7 +8693,7 @@
         <v>31000000</v>
       </c>
       <c r="H239" s="7" t="n">
-        <v>20666.67</v>
+        <v>48062.02</v>
       </c>
     </row>
     <row r="240">
@@ -8727,7 +8727,7 @@
         <v>93000000</v>
       </c>
       <c r="H240" s="7" t="n">
-        <v>62000</v>
+        <v>144186.05</v>
       </c>
     </row>
     <row r="241">
@@ -8761,7 +8761,7 @@
         <v>3100000</v>
       </c>
       <c r="H241" s="7" t="n">
-        <v>2066.67</v>
+        <v>4806.2</v>
       </c>
     </row>
     <row r="242">
@@ -8795,7 +8795,7 @@
         <v>15060000</v>
       </c>
       <c r="H242" s="7" t="n">
-        <v>10040</v>
+        <v>10189.45</v>
       </c>
     </row>
     <row r="243">
@@ -8829,7 +8829,7 @@
         <v>251000000</v>
       </c>
       <c r="H243" s="7" t="n">
-        <v>167333.33</v>
+        <v>169824.09</v>
       </c>
     </row>
     <row r="244">
@@ -8863,7 +8863,7 @@
         <v>753000000</v>
       </c>
       <c r="H244" s="7" t="n">
-        <v>502000</v>
+        <v>509472.26</v>
       </c>
     </row>
     <row r="245">
@@ -8897,7 +8897,7 @@
         <v>25100000</v>
       </c>
       <c r="H245" s="7" t="n">
-        <v>16733.33</v>
+        <v>16982.41</v>
       </c>
     </row>
     <row r="246">
@@ -8931,7 +8931,7 @@
         <v>3390000</v>
       </c>
       <c r="H246" s="7" t="n">
-        <v>2260</v>
+        <v>2293.64</v>
       </c>
     </row>
     <row r="247">
@@ -8965,7 +8965,7 @@
         <v>56500000</v>
       </c>
       <c r="H247" s="7" t="n">
-        <v>37666.67</v>
+        <v>38227.33</v>
       </c>
     </row>
     <row r="248">
@@ -8999,7 +8999,7 @@
         <v>169500000</v>
       </c>
       <c r="H248" s="7" t="n">
-        <v>113000</v>
+        <v>114682</v>
       </c>
     </row>
     <row r="249">
@@ -9033,7 +9033,7 @@
         <v>5650000</v>
       </c>
       <c r="H249" s="7" t="n">
-        <v>3766.67</v>
+        <v>3822.73</v>
       </c>
     </row>
     <row r="250">
@@ -9067,7 +9067,7 @@
         <v>2040000</v>
       </c>
       <c r="H250" s="7" t="n">
-        <v>1360</v>
+        <v>1380.24</v>
       </c>
     </row>
     <row r="251">
@@ -9101,7 +9101,7 @@
         <v>34000000</v>
       </c>
       <c r="H251" s="7" t="n">
-        <v>22666.67</v>
+        <v>23004.06</v>
       </c>
     </row>
     <row r="252">
@@ -9135,7 +9135,7 @@
         <v>102000000</v>
       </c>
       <c r="H252" s="7" t="n">
-        <v>68000</v>
+        <v>69012.17999999999</v>
       </c>
     </row>
     <row r="253">
@@ -9169,7 +9169,7 @@
         <v>3400000</v>
       </c>
       <c r="H253" s="7" t="n">
-        <v>2266.67</v>
+        <v>2300.41</v>
       </c>
     </row>
     <row r="254">
@@ -9203,7 +9203,7 @@
         <v>15270000</v>
       </c>
       <c r="H254" s="7" t="n">
-        <v>10180</v>
+        <v>10331.53</v>
       </c>
     </row>
     <row r="255">
@@ -9237,7 +9237,7 @@
         <v>254500000</v>
       </c>
       <c r="H255" s="7" t="n">
-        <v>169666.67</v>
+        <v>172192.15</v>
       </c>
     </row>
     <row r="256">
@@ -9271,7 +9271,7 @@
         <v>763500000</v>
       </c>
       <c r="H256" s="7" t="n">
-        <v>509000</v>
+        <v>516576.45</v>
       </c>
     </row>
     <row r="257">
@@ -9305,7 +9305,7 @@
         <v>25450000</v>
       </c>
       <c r="H257" s="7" t="n">
-        <v>16966.67</v>
+        <v>17219.22</v>
       </c>
     </row>
     <row r="258">
@@ -9339,7 +9339,7 @@
         <v>3420000</v>
       </c>
       <c r="H258" s="7" t="n">
-        <v>2280</v>
+        <v>2313.94</v>
       </c>
     </row>
     <row r="259">
@@ -9373,7 +9373,7 @@
         <v>57000000</v>
       </c>
       <c r="H259" s="7" t="n">
-        <v>38000</v>
+        <v>38565.63</v>
       </c>
     </row>
     <row r="260">
@@ -9407,7 +9407,7 @@
         <v>171000000</v>
       </c>
       <c r="H260" s="7" t="n">
-        <v>114000</v>
+        <v>115696.89</v>
       </c>
     </row>
     <row r="261">
@@ -9441,7 +9441,7 @@
         <v>5700000</v>
       </c>
       <c r="H261" s="7" t="n">
-        <v>3800</v>
+        <v>3856.56</v>
       </c>
     </row>
     <row r="262">
@@ -9475,7 +9475,7 @@
         <v>2040000</v>
       </c>
       <c r="H262" s="7" t="n">
-        <v>1360</v>
+        <v>1380.24</v>
       </c>
     </row>
     <row r="263">
@@ -9509,7 +9509,7 @@
         <v>34000000</v>
       </c>
       <c r="H263" s="7" t="n">
-        <v>22666.67</v>
+        <v>23004.06</v>
       </c>
     </row>
     <row r="264">
@@ -9543,7 +9543,7 @@
         <v>102000000</v>
       </c>
       <c r="H264" s="7" t="n">
-        <v>68000</v>
+        <v>69012.17999999999</v>
       </c>
     </row>
     <row r="265">
@@ -9577,7 +9577,7 @@
         <v>3400000</v>
       </c>
       <c r="H265" s="7" t="n">
-        <v>2266.67</v>
+        <v>2300.41</v>
       </c>
     </row>
     <row r="266">
@@ -9611,7 +9611,7 @@
         <v>15330000</v>
       </c>
       <c r="H266" s="7" t="n">
-        <v>10220</v>
+        <v>10372.12</v>
       </c>
     </row>
     <row r="267">
@@ -9645,7 +9645,7 @@
         <v>255500000</v>
       </c>
       <c r="H267" s="7" t="n">
-        <v>170333.33</v>
+        <v>172868.74</v>
       </c>
     </row>
     <row r="268">
@@ -9679,7 +9679,7 @@
         <v>766500000</v>
       </c>
       <c r="H268" s="7" t="n">
-        <v>511000</v>
+        <v>518606.22</v>
       </c>
     </row>
     <row r="269">
@@ -9713,7 +9713,7 @@
         <v>25550000</v>
       </c>
       <c r="H269" s="7" t="n">
-        <v>17033.33</v>
+        <v>17286.87</v>
       </c>
     </row>
     <row r="270">
@@ -9747,7 +9747,7 @@
         <v>3420000</v>
       </c>
       <c r="H270" s="7" t="n">
-        <v>2280</v>
+        <v>2313.94</v>
       </c>
     </row>
     <row r="271">
@@ -9781,7 +9781,7 @@
         <v>57000000</v>
       </c>
       <c r="H271" s="7" t="n">
-        <v>38000</v>
+        <v>38565.63</v>
       </c>
     </row>
     <row r="272">
@@ -9815,7 +9815,7 @@
         <v>171000000</v>
       </c>
       <c r="H272" s="7" t="n">
-        <v>114000</v>
+        <v>115696.89</v>
       </c>
     </row>
     <row r="273">
@@ -9849,7 +9849,7 @@
         <v>5700000</v>
       </c>
       <c r="H273" s="7" t="n">
-        <v>3800</v>
+        <v>3856.56</v>
       </c>
     </row>
     <row r="274">
@@ -9883,7 +9883,7 @@
         <v>2100000</v>
       </c>
       <c r="H274" s="7" t="n">
-        <v>1400</v>
+        <v>1420.84</v>
       </c>
     </row>
     <row r="275">
@@ -9917,7 +9917,7 @@
         <v>35000000</v>
       </c>
       <c r="H275" s="7" t="n">
-        <v>23333.33</v>
+        <v>23680.65</v>
       </c>
     </row>
     <row r="276">
@@ -9951,7 +9951,7 @@
         <v>105000000</v>
       </c>
       <c r="H276" s="7" t="n">
-        <v>70000</v>
+        <v>71041.95</v>
       </c>
     </row>
     <row r="277">
@@ -9985,7 +9985,7 @@
         <v>3500000</v>
       </c>
       <c r="H277" s="7" t="n">
-        <v>2333.33</v>
+        <v>2368.06</v>
       </c>
     </row>
     <row r="278">
@@ -10019,7 +10019,7 @@
         <v>15390000</v>
       </c>
       <c r="H278" s="7" t="n">
-        <v>10260</v>
+        <v>10412.72</v>
       </c>
     </row>
     <row r="279">
@@ -10053,7 +10053,7 @@
         <v>256500000</v>
       </c>
       <c r="H279" s="7" t="n">
-        <v>171000</v>
+        <v>173545.33</v>
       </c>
     </row>
     <row r="280">
@@ -10087,7 +10087,7 @@
         <v>769500000</v>
       </c>
       <c r="H280" s="7" t="n">
-        <v>513000</v>
+        <v>520635.99</v>
       </c>
     </row>
     <row r="281">
@@ -10121,7 +10121,7 @@
         <v>25650000</v>
       </c>
       <c r="H281" s="7" t="n">
-        <v>17100</v>
+        <v>17354.53</v>
       </c>
     </row>
     <row r="282">
@@ -10155,7 +10155,7 @@
         <v>3510000</v>
       </c>
       <c r="H282" s="7" t="n">
-        <v>2340</v>
+        <v>2374.83</v>
       </c>
     </row>
     <row r="283">
@@ -10189,7 +10189,7 @@
         <v>58500000</v>
       </c>
       <c r="H283" s="7" t="n">
-        <v>39000</v>
+        <v>39580.51</v>
       </c>
     </row>
     <row r="284">
@@ -10223,7 +10223,7 @@
         <v>175500000</v>
       </c>
       <c r="H284" s="7" t="n">
-        <v>117000</v>
+        <v>118741.54</v>
       </c>
     </row>
     <row r="285">
@@ -10257,7 +10257,7 @@
         <v>5850000</v>
       </c>
       <c r="H285" s="7" t="n">
-        <v>3900</v>
+        <v>3958.05</v>
       </c>
     </row>
     <row r="286">
@@ -10291,7 +10291,7 @@
         <v>2130000</v>
       </c>
       <c r="H286" s="7" t="n">
-        <v>1420</v>
+        <v>1441.14</v>
       </c>
     </row>
     <row r="287">
@@ -10325,7 +10325,7 @@
         <v>35500000</v>
       </c>
       <c r="H287" s="7" t="n">
-        <v>23666.67</v>
+        <v>24018.94</v>
       </c>
     </row>
     <row r="288">
@@ -10359,7 +10359,7 @@
         <v>106500000</v>
       </c>
       <c r="H288" s="7" t="n">
-        <v>71000</v>
+        <v>72056.83</v>
       </c>
     </row>
     <row r="289">
@@ -10393,7 +10393,7 @@
         <v>3550000</v>
       </c>
       <c r="H289" s="7" t="n">
-        <v>2366.67</v>
+        <v>2401.89</v>
       </c>
     </row>
     <row r="290">
@@ -10427,7 +10427,7 @@
         <v>15450000</v>
       </c>
       <c r="H290" s="7" t="n">
-        <v>10300</v>
+        <v>10098.04</v>
       </c>
     </row>
     <row r="291">
@@ -10461,7 +10461,7 @@
         <v>257500000</v>
       </c>
       <c r="H291" s="7" t="n">
-        <v>171666.67</v>
+        <v>168300.65</v>
       </c>
     </row>
     <row r="292">
@@ -10495,7 +10495,7 @@
         <v>772500000</v>
       </c>
       <c r="H292" s="7" t="n">
-        <v>515000</v>
+        <v>504901.96</v>
       </c>
     </row>
     <row r="293">
@@ -10529,7 +10529,7 @@
         <v>25750000</v>
       </c>
       <c r="H293" s="7" t="n">
-        <v>17166.67</v>
+        <v>16830.07</v>
       </c>
     </row>
     <row r="294">
@@ -10563,7 +10563,7 @@
         <v>3540000</v>
       </c>
       <c r="H294" s="7" t="n">
-        <v>2360</v>
+        <v>2313.73</v>
       </c>
     </row>
     <row r="295">
@@ -10597,7 +10597,7 @@
         <v>59000000</v>
       </c>
       <c r="H295" s="7" t="n">
-        <v>39333.33</v>
+        <v>38562.09</v>
       </c>
     </row>
     <row r="296">
@@ -10631,7 +10631,7 @@
         <v>177000000</v>
       </c>
       <c r="H296" s="7" t="n">
-        <v>118000</v>
+        <v>115686.27</v>
       </c>
     </row>
     <row r="297">
@@ -10665,7 +10665,7 @@
         <v>5900000</v>
       </c>
       <c r="H297" s="7" t="n">
-        <v>3933.33</v>
+        <v>3856.21</v>
       </c>
     </row>
     <row r="298">
@@ -10699,7 +10699,7 @@
         <v>2190000</v>
       </c>
       <c r="H298" s="7" t="n">
-        <v>1460</v>
+        <v>1431.37</v>
       </c>
     </row>
     <row r="299">
@@ -10733,7 +10733,7 @@
         <v>36500000</v>
       </c>
       <c r="H299" s="7" t="n">
-        <v>24333.33</v>
+        <v>23856.21</v>
       </c>
     </row>
     <row r="300">
@@ -10767,7 +10767,7 @@
         <v>109500000</v>
       </c>
       <c r="H300" s="7" t="n">
-        <v>73000</v>
+        <v>71568.63</v>
       </c>
     </row>
     <row r="301">
@@ -10801,7 +10801,7 @@
         <v>3650000</v>
       </c>
       <c r="H301" s="7" t="n">
-        <v>2433.33</v>
+        <v>2385.62</v>
       </c>
     </row>
     <row r="302">
@@ -10835,7 +10835,7 @@
         <v>15600000</v>
       </c>
       <c r="H302" s="7" t="n">
-        <v>10400</v>
+        <v>10196.08</v>
       </c>
     </row>
     <row r="303">
@@ -10869,7 +10869,7 @@
         <v>260000000</v>
       </c>
       <c r="H303" s="7" t="n">
-        <v>173333.33</v>
+        <v>169934.64</v>
       </c>
     </row>
     <row r="304">
@@ -10903,7 +10903,7 @@
         <v>780000000</v>
       </c>
       <c r="H304" s="7" t="n">
-        <v>520000</v>
+        <v>509803.92</v>
       </c>
     </row>
     <row r="305">
@@ -10937,7 +10937,7 @@
         <v>26000000</v>
       </c>
       <c r="H305" s="7" t="n">
-        <v>17333.33</v>
+        <v>16993.46</v>
       </c>
     </row>
     <row r="306">
@@ -10971,7 +10971,7 @@
         <v>3570000</v>
       </c>
       <c r="H306" s="7" t="n">
-        <v>2380</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="307">
@@ -11005,7 +11005,7 @@
         <v>59500000</v>
       </c>
       <c r="H307" s="7" t="n">
-        <v>39666.67</v>
+        <v>38888.89</v>
       </c>
     </row>
     <row r="308">
@@ -11039,7 +11039,7 @@
         <v>178500000</v>
       </c>
       <c r="H308" s="7" t="n">
-        <v>119000</v>
+        <v>116666.67</v>
       </c>
     </row>
     <row r="309">
@@ -11073,7 +11073,7 @@
         <v>5950000</v>
       </c>
       <c r="H309" s="7" t="n">
-        <v>3966.67</v>
+        <v>3888.89</v>
       </c>
     </row>
     <row r="310">
@@ -11107,7 +11107,7 @@
         <v>2280000</v>
       </c>
       <c r="H310" s="7" t="n">
-        <v>1520</v>
+        <v>1490.2</v>
       </c>
     </row>
     <row r="311">
@@ -11141,7 +11141,7 @@
         <v>38000000</v>
       </c>
       <c r="H311" s="7" t="n">
-        <v>25333.33</v>
+        <v>24836.6</v>
       </c>
     </row>
     <row r="312">
@@ -11175,7 +11175,7 @@
         <v>114000000</v>
       </c>
       <c r="H312" s="7" t="n">
-        <v>76000</v>
+        <v>74509.8</v>
       </c>
     </row>
     <row r="313">
@@ -11209,7 +11209,7 @@
         <v>3800000</v>
       </c>
       <c r="H313" s="7" t="n">
-        <v>2533.33</v>
+        <v>2483.66</v>
       </c>
     </row>
     <row r="314">
@@ -11243,7 +11243,7 @@
         <v>15660000</v>
       </c>
       <c r="H314" s="7" t="n">
-        <v>10440</v>
+        <v>10235.29</v>
       </c>
     </row>
     <row r="315">
@@ -11277,7 +11277,7 @@
         <v>261000000</v>
       </c>
       <c r="H315" s="7" t="n">
-        <v>174000</v>
+        <v>170588.24</v>
       </c>
     </row>
     <row r="316">
@@ -11311,7 +11311,7 @@
         <v>783000000</v>
       </c>
       <c r="H316" s="7" t="n">
-        <v>522000</v>
+        <v>511764.71</v>
       </c>
     </row>
     <row r="317">
@@ -11345,7 +11345,7 @@
         <v>26100000</v>
       </c>
       <c r="H317" s="7" t="n">
-        <v>17400</v>
+        <v>17058.82</v>
       </c>
     </row>
     <row r="318">
@@ -11379,7 +11379,7 @@
         <v>3600000</v>
       </c>
       <c r="H318" s="7" t="n">
-        <v>2400</v>
+        <v>2352.94</v>
       </c>
     </row>
     <row r="319">
@@ -11413,7 +11413,7 @@
         <v>60000000</v>
       </c>
       <c r="H319" s="7" t="n">
-        <v>40000</v>
+        <v>39215.69</v>
       </c>
     </row>
     <row r="320">
@@ -11447,7 +11447,7 @@
         <v>180000000</v>
       </c>
       <c r="H320" s="7" t="n">
-        <v>120000</v>
+        <v>117647.06</v>
       </c>
     </row>
     <row r="321">
@@ -11481,7 +11481,7 @@
         <v>6000000</v>
       </c>
       <c r="H321" s="7" t="n">
-        <v>4000</v>
+        <v>3921.57</v>
       </c>
     </row>
     <row r="322">
@@ -11515,7 +11515,7 @@
         <v>2310000</v>
       </c>
       <c r="H322" s="7" t="n">
-        <v>1540</v>
+        <v>1509.8</v>
       </c>
     </row>
     <row r="323">
@@ -11549,7 +11549,7 @@
         <v>38500000</v>
       </c>
       <c r="H323" s="7" t="n">
-        <v>25666.67</v>
+        <v>25163.4</v>
       </c>
     </row>
     <row r="324">
@@ -11583,7 +11583,7 @@
         <v>115500000</v>
       </c>
       <c r="H324" s="7" t="n">
-        <v>77000</v>
+        <v>75490.2</v>
       </c>
     </row>
     <row r="325">
@@ -11617,7 +11617,7 @@
         <v>3850000</v>
       </c>
       <c r="H325" s="7" t="n">
-        <v>2566.67</v>
+        <v>2516.34</v>
       </c>
     </row>
     <row r="326">
@@ -11651,7 +11651,7 @@
         <v>15690000</v>
       </c>
       <c r="H326" s="7" t="n">
-        <v>10460</v>
+        <v>10254.9</v>
       </c>
     </row>
     <row r="327">
@@ -11685,7 +11685,7 @@
         <v>261500000</v>
       </c>
       <c r="H327" s="7" t="n">
-        <v>174333.33</v>
+        <v>170915.03</v>
       </c>
     </row>
     <row r="328">
@@ -11719,7 +11719,7 @@
         <v>784500000</v>
       </c>
       <c r="H328" s="7" t="n">
-        <v>523000</v>
+        <v>512745.1</v>
       </c>
     </row>
     <row r="329">
@@ -11753,7 +11753,7 @@
         <v>26150000</v>
       </c>
       <c r="H329" s="7" t="n">
-        <v>17433.33</v>
+        <v>17091.5</v>
       </c>
     </row>
     <row r="330">
@@ -11787,7 +11787,7 @@
         <v>3600000</v>
       </c>
       <c r="H330" s="7" t="n">
-        <v>2400</v>
+        <v>2352.94</v>
       </c>
     </row>
     <row r="331">
@@ -11821,7 +11821,7 @@
         <v>60000000</v>
       </c>
       <c r="H331" s="7" t="n">
-        <v>40000</v>
+        <v>39215.69</v>
       </c>
     </row>
     <row r="332">
@@ -11855,7 +11855,7 @@
         <v>180000000</v>
       </c>
       <c r="H332" s="7" t="n">
-        <v>120000</v>
+        <v>117647.06</v>
       </c>
     </row>
     <row r="333">
@@ -11889,7 +11889,7 @@
         <v>6000000</v>
       </c>
       <c r="H333" s="7" t="n">
-        <v>4000</v>
+        <v>3921.57</v>
       </c>
     </row>
     <row r="334">
@@ -11923,7 +11923,7 @@
         <v>2340000</v>
       </c>
       <c r="H334" s="7" t="n">
-        <v>1560</v>
+        <v>1529.41</v>
       </c>
     </row>
     <row r="335">
@@ -11957,7 +11957,7 @@
         <v>39000000</v>
       </c>
       <c r="H335" s="7" t="n">
-        <v>26000</v>
+        <v>25490.2</v>
       </c>
     </row>
     <row r="336">
@@ -11991,7 +11991,7 @@
         <v>117000000</v>
       </c>
       <c r="H336" s="7" t="n">
-        <v>78000</v>
+        <v>76470.59</v>
       </c>
     </row>
     <row r="337">
@@ -12025,7 +12025,7 @@
         <v>3900000</v>
       </c>
       <c r="H337" s="7" t="n">
-        <v>2600</v>
+        <v>2549.02</v>
       </c>
     </row>
     <row r="338">
@@ -12059,7 +12059,7 @@
         <v>15720000</v>
       </c>
       <c r="H338" s="7" t="n">
-        <v>10480</v>
+        <v>10274.51</v>
       </c>
     </row>
     <row r="339">
@@ -12093,7 +12093,7 @@
         <v>262000000</v>
       </c>
       <c r="H339" s="7" t="n">
-        <v>174666.67</v>
+        <v>171241.83</v>
       </c>
     </row>
     <row r="340">
@@ -12127,7 +12127,7 @@
         <v>786000000</v>
       </c>
       <c r="H340" s="7" t="n">
-        <v>524000</v>
+        <v>513725.49</v>
       </c>
     </row>
     <row r="341">
@@ -12161,7 +12161,7 @@
         <v>26200000</v>
       </c>
       <c r="H341" s="7" t="n">
-        <v>17466.67</v>
+        <v>17124.18</v>
       </c>
     </row>
     <row r="342">
@@ -12195,7 +12195,7 @@
         <v>3630000</v>
       </c>
       <c r="H342" s="7" t="n">
-        <v>2420</v>
+        <v>2372.55</v>
       </c>
     </row>
     <row r="343">
@@ -12229,7 +12229,7 @@
         <v>60500000</v>
       </c>
       <c r="H343" s="7" t="n">
-        <v>40333.33</v>
+        <v>39542.48</v>
       </c>
     </row>
     <row r="344">
@@ -12263,7 +12263,7 @@
         <v>181500000</v>
       </c>
       <c r="H344" s="7" t="n">
-        <v>121000</v>
+        <v>118627.45</v>
       </c>
     </row>
     <row r="345">
@@ -12297,7 +12297,7 @@
         <v>6050000</v>
       </c>
       <c r="H345" s="7" t="n">
-        <v>4033.33</v>
+        <v>3954.25</v>
       </c>
     </row>
     <row r="346">
@@ -12331,7 +12331,7 @@
         <v>2370000</v>
       </c>
       <c r="H346" s="7" t="n">
-        <v>1580</v>
+        <v>1549.02</v>
       </c>
     </row>
     <row r="347">
@@ -12365,7 +12365,7 @@
         <v>39500000</v>
       </c>
       <c r="H347" s="7" t="n">
-        <v>26333.33</v>
+        <v>25816.99</v>
       </c>
     </row>
     <row r="348">
@@ -12399,7 +12399,7 @@
         <v>118500000</v>
       </c>
       <c r="H348" s="7" t="n">
-        <v>79000</v>
+        <v>77450.98</v>
       </c>
     </row>
     <row r="349">
@@ -12433,7 +12433,7 @@
         <v>3950000</v>
       </c>
       <c r="H349" s="7" t="n">
-        <v>2633.33</v>
+        <v>2581.7</v>
       </c>
     </row>
     <row r="350">
@@ -12467,7 +12467,7 @@
         <v>15720000</v>
       </c>
       <c r="H350" s="7" t="n">
-        <v>10480</v>
+        <v>10274.51</v>
       </c>
     </row>
     <row r="351">
@@ -12501,7 +12501,7 @@
         <v>262000000</v>
       </c>
       <c r="H351" s="7" t="n">
-        <v>174666.67</v>
+        <v>171241.83</v>
       </c>
     </row>
     <row r="352">
@@ -12535,7 +12535,7 @@
         <v>786000000</v>
       </c>
       <c r="H352" s="7" t="n">
-        <v>524000</v>
+        <v>513725.49</v>
       </c>
     </row>
     <row r="353">
@@ -12569,7 +12569,7 @@
         <v>26200000</v>
       </c>
       <c r="H353" s="7" t="n">
-        <v>17466.67</v>
+        <v>17124.18</v>
       </c>
     </row>
     <row r="354">
@@ -12603,7 +12603,7 @@
         <v>3630000</v>
       </c>
       <c r="H354" s="7" t="n">
-        <v>2420</v>
+        <v>2372.55</v>
       </c>
     </row>
     <row r="355">
@@ -12637,7 +12637,7 @@
         <v>60500000</v>
       </c>
       <c r="H355" s="7" t="n">
-        <v>40333.33</v>
+        <v>39542.48</v>
       </c>
     </row>
     <row r="356">
@@ -12671,7 +12671,7 @@
         <v>181500000</v>
       </c>
       <c r="H356" s="7" t="n">
-        <v>121000</v>
+        <v>118627.45</v>
       </c>
     </row>
     <row r="357">
@@ -12705,7 +12705,7 @@
         <v>6050000</v>
       </c>
       <c r="H357" s="7" t="n">
-        <v>4033.33</v>
+        <v>3954.25</v>
       </c>
     </row>
     <row r="358">
@@ -12739,7 +12739,7 @@
         <v>2430000</v>
       </c>
       <c r="H358" s="7" t="n">
-        <v>1620</v>
+        <v>1588.24</v>
       </c>
     </row>
     <row r="359">
@@ -12773,7 +12773,7 @@
         <v>40500000</v>
       </c>
       <c r="H359" s="7" t="n">
-        <v>27000</v>
+        <v>26470.59</v>
       </c>
     </row>
     <row r="360">
@@ -12807,7 +12807,7 @@
         <v>121500000</v>
       </c>
       <c r="H360" s="7" t="n">
-        <v>81000</v>
+        <v>79411.75999999999</v>
       </c>
     </row>
     <row r="361">
@@ -12841,7 +12841,7 @@
         <v>4050000</v>
       </c>
       <c r="H361" s="7" t="n">
-        <v>2700</v>
+        <v>2647.06</v>
       </c>
     </row>
     <row r="362">
@@ -12875,7 +12875,7 @@
         <v>15720000</v>
       </c>
       <c r="H362" s="7" t="n">
-        <v>10480</v>
+        <v>10274.51</v>
       </c>
     </row>
     <row r="363">
@@ -12909,7 +12909,7 @@
         <v>262000000</v>
       </c>
       <c r="H363" s="7" t="n">
-        <v>174666.67</v>
+        <v>171241.83</v>
       </c>
     </row>
     <row r="364">
@@ -12943,7 +12943,7 @@
         <v>786000000</v>
       </c>
       <c r="H364" s="7" t="n">
-        <v>524000</v>
+        <v>513725.49</v>
       </c>
     </row>
     <row r="365">
@@ -12977,7 +12977,7 @@
         <v>26200000</v>
       </c>
       <c r="H365" s="7" t="n">
-        <v>17466.67</v>
+        <v>17124.18</v>
       </c>
     </row>
     <row r="366">
@@ -13011,7 +13011,7 @@
         <v>3630000</v>
       </c>
       <c r="H366" s="7" t="n">
-        <v>2420</v>
+        <v>2372.55</v>
       </c>
     </row>
     <row r="367">
@@ -13045,7 +13045,7 @@
         <v>60500000</v>
       </c>
       <c r="H367" s="7" t="n">
-        <v>40333.33</v>
+        <v>39542.48</v>
       </c>
     </row>
     <row r="368">
@@ -13079,7 +13079,7 @@
         <v>181500000</v>
       </c>
       <c r="H368" s="7" t="n">
-        <v>121000</v>
+        <v>118627.45</v>
       </c>
     </row>
     <row r="369">
@@ -13113,7 +13113,7 @@
         <v>6050000</v>
       </c>
       <c r="H369" s="7" t="n">
-        <v>4033.33</v>
+        <v>3954.25</v>
       </c>
     </row>
     <row r="370">
@@ -13147,7 +13147,7 @@
         <v>2430000</v>
       </c>
       <c r="H370" s="7" t="n">
-        <v>1620</v>
+        <v>1588.24</v>
       </c>
     </row>
     <row r="371">
@@ -13181,7 +13181,7 @@
         <v>40500000</v>
       </c>
       <c r="H371" s="7" t="n">
-        <v>27000</v>
+        <v>26470.59</v>
       </c>
     </row>
     <row r="372">
@@ -13215,7 +13215,7 @@
         <v>121500000</v>
       </c>
       <c r="H372" s="7" t="n">
-        <v>81000</v>
+        <v>79411.75999999999</v>
       </c>
     </row>
     <row r="373">
@@ -13249,7 +13249,7 @@
         <v>4050000</v>
       </c>
       <c r="H373" s="7" t="n">
-        <v>2700</v>
+        <v>2647.06</v>
       </c>
     </row>
   </sheetData>
@@ -13320,7 +13320,7 @@
         <v>470080000</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>313386.66</v>
+        <v>1531604.33</v>
       </c>
     </row>
     <row r="3">
@@ -13341,7 +13341,7 @@
         <v>83200000</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>55466.66</v>
+        <v>271080.41</v>
       </c>
     </row>
     <row r="4">
@@ -13362,7 +13362,7 @@
         <v>35360000</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>23573.34</v>
+        <v>115209.17</v>
       </c>
     </row>
     <row r="5">
@@ -13383,7 +13383,7 @@
         <v>659360000</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>439573.34</v>
+        <v>2148312.26</v>
       </c>
     </row>
     <row r="6">
@@ -13404,7 +13404,7 @@
         <v>147680000</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>98453.34</v>
+        <v>481167.73</v>
       </c>
     </row>
     <row r="7">
@@ -13425,7 +13425,7 @@
         <v>70720000</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>47146.66</v>
+        <v>230418.35</v>
       </c>
     </row>
     <row r="8">
@@ -13446,7 +13446,7 @@
         <v>723840000</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>482560</v>
+        <v>2358399.59</v>
       </c>
     </row>
     <row r="9">
@@ -13467,7 +13467,7 @@
         <v>174720000</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>116480</v>
+        <v>569268.87</v>
       </c>
     </row>
     <row r="10">
@@ -13488,7 +13488,7 @@
         <v>81120000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>54080</v>
+        <v>264303.4</v>
       </c>
     </row>
     <row r="11">
@@ -13509,7 +13509,7 @@
         <v>736320000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>490880</v>
+        <v>2399061.64</v>
       </c>
     </row>
     <row r="12">
@@ -13530,7 +13530,7 @@
         <v>176800000</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>117866.66</v>
+        <v>576045.88</v>
       </c>
     </row>
     <row r="13">
@@ -13551,7 +13551,7 @@
         <v>85280000</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>56853.34</v>
+        <v>277857.42</v>
       </c>
     </row>
     <row r="14">
@@ -13572,7 +13572,7 @@
         <v>750880000</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>500586.66</v>
+        <v>2092695.3</v>
       </c>
     </row>
     <row r="15">
@@ -13593,7 +13593,7 @@
         <v>178880000</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>119253.34</v>
+        <v>498536.83</v>
       </c>
     </row>
     <row r="16">
@@ -13614,7 +13614,7 @@
         <v>85280000</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>56853.34</v>
+        <v>237674.54</v>
       </c>
     </row>
     <row r="17">
@@ -13635,7 +13635,7 @@
         <v>802880000</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>535253.34</v>
+        <v>2237618.79</v>
       </c>
     </row>
     <row r="18">
@@ -13656,7 +13656,7 @@
         <v>193440000</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>128960</v>
+        <v>539115.41</v>
       </c>
     </row>
     <row r="19">
@@ -13677,7 +13677,7 @@
         <v>89440000</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>59626.66</v>
+        <v>249268.42</v>
       </c>
     </row>
     <row r="20">
@@ -13698,7 +13698,7 @@
         <v>848640000</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>565760</v>
+        <v>2365151.47</v>
       </c>
     </row>
     <row r="21">
@@ -13719,7 +13719,7 @@
         <v>197600000</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>131733.34</v>
+        <v>550709.28</v>
       </c>
     </row>
     <row r="22">
@@ -13740,7 +13740,7 @@
         <v>95680000</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>63786.66</v>
+        <v>266659.24</v>
       </c>
     </row>
     <row r="23">
@@ -13755,13 +13755,13 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>873600000</v>
+        <v>871520000</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>582400</v>
+        <v>2428917.81</v>
       </c>
     </row>
     <row r="24">
@@ -13782,7 +13782,7 @@
         <v>203840000</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>135893.34</v>
+        <v>568100.11</v>
       </c>
     </row>
     <row r="25">
@@ -13803,7 +13803,7 @@
         <v>95680000</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>63786.66</v>
+        <v>266659.24</v>
       </c>
     </row>
     <row r="26">
@@ -13824,7 +13824,7 @@
         <v>886080000</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>590720</v>
+        <v>2208849.56</v>
       </c>
     </row>
     <row r="27">
@@ -13845,7 +13845,7 @@
         <v>210080000</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>140053.34</v>
+        <v>523694.38</v>
       </c>
     </row>
     <row r="28">
@@ -13866,7 +13866,7 @@
         <v>97760000</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>65173.34</v>
+        <v>243699.36</v>
       </c>
     </row>
     <row r="29">
@@ -13887,7 +13887,7 @@
         <v>904800000</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>603200</v>
+        <v>2255515.39</v>
       </c>
     </row>
     <row r="30">
@@ -13908,7 +13908,7 @@
         <v>212160000</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>141440</v>
+        <v>528879.48</v>
       </c>
     </row>
     <row r="31">
@@ -13929,7 +13929,7 @@
         <v>101920000</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>67946.66</v>
+        <v>254069.54</v>
       </c>
     </row>
     <row r="32">
@@ -13950,7 +13950,7 @@
         <v>911040000</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>607360</v>
+        <v>2271070.67</v>
       </c>
     </row>
     <row r="33">
@@ -13971,7 +13971,7 @@
         <v>218400000</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>145600</v>
+        <v>544434.74</v>
       </c>
     </row>
     <row r="34">
@@ -13992,7 +13992,7 @@
         <v>106080000</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>70720</v>
+        <v>264439.72</v>
       </c>
     </row>
     <row r="35">
@@ -14013,7 +14013,7 @@
         <v>938080000</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>625386.66</v>
+        <v>2338476.89</v>
       </c>
     </row>
     <row r="36">
@@ -14034,7 +14034,7 @@
         <v>218400000</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>145600</v>
+        <v>544434.74</v>
       </c>
     </row>
     <row r="37">
@@ -14055,7 +14055,7 @@
         <v>112320000</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>74880</v>
+        <v>279995.01</v>
       </c>
     </row>
     <row r="38">
@@ -14076,7 +14076,7 @@
         <v>950560000</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>633706.66</v>
+        <v>2231466.27</v>
       </c>
     </row>
     <row r="39">
@@ -14097,7 +14097,7 @@
         <v>222560000</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>148373.34</v>
+        <v>522465.85</v>
       </c>
     </row>
     <row r="40">
@@ -14118,7 +14118,7 @@
         <v>112320000</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>74880</v>
+        <v>263674.36</v>
       </c>
     </row>
     <row r="41">
@@ -14139,7 +14139,7 @@
         <v>958880000</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>639253.34</v>
+        <v>2250997.7</v>
       </c>
     </row>
     <row r="42">
@@ -14160,7 +14160,7 @@
         <v>222560000</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>148373.34</v>
+        <v>522465.85</v>
       </c>
     </row>
     <row r="43">
@@ -14181,7 +14181,7 @@
         <v>120640000</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>80426.66</v>
+        <v>283205.78</v>
       </c>
     </row>
     <row r="44">
@@ -14196,13 +14196,13 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>981760000</v>
+        <v>979680000</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>654506.66</v>
+        <v>2299826.29</v>
       </c>
     </row>
     <row r="45">
@@ -14223,7 +14223,7 @@
         <v>226720000</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>151146.66</v>
+        <v>532231.5699999999</v>
       </c>
     </row>
     <row r="46">
@@ -14244,7 +14244,7 @@
         <v>120640000</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>80426.66</v>
+        <v>283205.78</v>
       </c>
     </row>
     <row r="47">
@@ -14259,13 +14259,13 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>994240000</v>
+        <v>992160000</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>662826.66</v>
+        <v>2329123.43</v>
       </c>
     </row>
     <row r="48">
@@ -14286,7 +14286,7 @@
         <v>230880000</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>153920</v>
+        <v>541997.28</v>
       </c>
     </row>
     <row r="49">
@@ -14307,7 +14307,7 @@
         <v>118560000</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>79040</v>
+        <v>278322.92</v>
       </c>
     </row>
     <row r="50">
@@ -14328,7 +14328,7 @@
         <v>1006720000</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>671146.66</v>
+        <v>1560806.21</v>
       </c>
     </row>
     <row r="51">
@@ -14349,7 +14349,7 @@
         <v>228800000</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>152533.34</v>
+        <v>354728.68</v>
       </c>
     </row>
     <row r="52">
@@ -14370,7 +14370,7 @@
         <v>124800000</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>83200</v>
+        <v>193488.37</v>
       </c>
     </row>
     <row r="53">
@@ -14391,7 +14391,7 @@
         <v>1027520000</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>685013.34</v>
+        <v>1593054.26</v>
       </c>
     </row>
     <row r="54">
@@ -14412,7 +14412,7 @@
         <v>235040000</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>156693.34</v>
+        <v>364403.1</v>
       </c>
     </row>
     <row r="55">
@@ -14433,7 +14433,7 @@
         <v>128960000</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>85973.34</v>
+        <v>199937.99</v>
       </c>
     </row>
     <row r="56">
@@ -14454,7 +14454,7 @@
         <v>1025440000</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>683626.66</v>
+        <v>1589829.45</v>
       </c>
     </row>
     <row r="57">
@@ -14475,7 +14475,7 @@
         <v>235040000</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>156693.34</v>
+        <v>364403.1</v>
       </c>
     </row>
     <row r="58">
@@ -14496,7 +14496,7 @@
         <v>128960000</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>85973.34</v>
+        <v>199937.99</v>
       </c>
     </row>
     <row r="59">
@@ -14517,7 +14517,7 @@
         <v>1031680000</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>687786.66</v>
+        <v>1599503.87</v>
       </c>
     </row>
     <row r="60">
@@ -14538,7 +14538,7 @@
         <v>235040000</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>156693.34</v>
+        <v>364403.1</v>
       </c>
     </row>
     <row r="61">
@@ -14559,7 +14559,7 @@
         <v>128960000</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>85973.34</v>
+        <v>199937.99</v>
       </c>
     </row>
     <row r="62">
@@ -14580,7 +14580,7 @@
         <v>1044160000</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>696106.66</v>
+        <v>706468.21</v>
       </c>
     </row>
     <row r="63">
@@ -14601,7 +14601,7 @@
         <v>235040000</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>156693.34</v>
+        <v>159025.7</v>
       </c>
     </row>
     <row r="64">
@@ -14622,7 +14622,7 @@
         <v>141440000</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>94293.34</v>
+        <v>95696.89</v>
       </c>
     </row>
     <row r="65">
@@ -14643,7 +14643,7 @@
         <v>1058720000</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>705813.34</v>
+        <v>716319.35</v>
       </c>
     </row>
     <row r="66">
@@ -14664,7 +14664,7 @@
         <v>237120000</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>158080</v>
+        <v>160433.02</v>
       </c>
     </row>
     <row r="67">
@@ -14685,7 +14685,7 @@
         <v>141440000</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>94293.34</v>
+        <v>95696.89</v>
       </c>
     </row>
     <row r="68">
@@ -14706,7 +14706,7 @@
         <v>1062880000</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>708586.66</v>
+        <v>719133.95</v>
       </c>
     </row>
     <row r="69">
@@ -14727,7 +14727,7 @@
         <v>237120000</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>158080</v>
+        <v>160433.02</v>
       </c>
     </row>
     <row r="70">
@@ -14748,7 +14748,7 @@
         <v>145600000</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>97066.66</v>
+        <v>98511.5</v>
       </c>
     </row>
     <row r="71">
@@ -14769,7 +14769,7 @@
         <v>1067040000</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>711360</v>
+        <v>721948.5699999999</v>
       </c>
     </row>
     <row r="72">
@@ -14790,7 +14790,7 @@
         <v>243360000</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>162240</v>
+        <v>164654.93</v>
       </c>
     </row>
     <row r="73">
@@ -14811,7 +14811,7 @@
         <v>147680000</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>98453.34</v>
+        <v>99918.8</v>
       </c>
     </row>
     <row r="74">
@@ -14832,7 +14832,7 @@
         <v>1071200000</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>714133.34</v>
+        <v>700130.72</v>
       </c>
     </row>
     <row r="75">
@@ -14853,7 +14853,7 @@
         <v>245440000</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>163626.66</v>
+        <v>160418.3</v>
       </c>
     </row>
     <row r="76">
@@ -14874,7 +14874,7 @@
         <v>151840000</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>101226.66</v>
+        <v>99241.83</v>
       </c>
     </row>
     <row r="77">
@@ -14895,7 +14895,7 @@
         <v>1081600000</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>721066.66</v>
+        <v>706928.1</v>
       </c>
     </row>
     <row r="78">
@@ -14916,7 +14916,7 @@
         <v>247520000</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>165013.34</v>
+        <v>161777.78</v>
       </c>
     </row>
     <row r="79">
@@ -14937,7 +14937,7 @@
         <v>158080000</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>105386.66</v>
+        <v>103320.26</v>
       </c>
     </row>
     <row r="80">
@@ -14958,7 +14958,7 @@
         <v>1085760000</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>723840</v>
+        <v>709647.0600000001</v>
       </c>
     </row>
     <row r="81">
@@ -14979,7 +14979,7 @@
         <v>249600000</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>166400</v>
+        <v>163137.26</v>
       </c>
     </row>
     <row r="82">
@@ -15000,7 +15000,7 @@
         <v>160160000</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>106773.34</v>
+        <v>104679.74</v>
       </c>
     </row>
     <row r="83">
@@ -15021,7 +15021,7 @@
         <v>1087840000</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>725226.66</v>
+        <v>711006.53</v>
       </c>
     </row>
     <row r="84">
@@ -15042,7 +15042,7 @@
         <v>249600000</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>166400</v>
+        <v>163137.26</v>
       </c>
     </row>
     <row r="85">
@@ -15063,7 +15063,7 @@
         <v>162240000</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>108160</v>
+        <v>106039.22</v>
       </c>
     </row>
     <row r="86">
@@ -15084,7 +15084,7 @@
         <v>1089920000</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>726613.34</v>
+        <v>712366.01</v>
       </c>
     </row>
     <row r="87">
@@ -15105,7 +15105,7 @@
         <v>251680000</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>167786.66</v>
+        <v>164496.73</v>
       </c>
     </row>
     <row r="88">
@@ -15126,7 +15126,7 @@
         <v>164320000</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>109546.66</v>
+        <v>107398.69</v>
       </c>
     </row>
     <row r="89">
@@ -15147,7 +15147,7 @@
         <v>1089920000</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>726613.34</v>
+        <v>712366.01</v>
       </c>
     </row>
     <row r="90">
@@ -15168,7 +15168,7 @@
         <v>251680000</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>167786.66</v>
+        <v>164496.73</v>
       </c>
     </row>
     <row r="91">
@@ -15189,7 +15189,7 @@
         <v>168480000</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>112320</v>
+        <v>110117.65</v>
       </c>
     </row>
     <row r="92">
@@ -15210,7 +15210,7 @@
         <v>1089920000</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>726613.34</v>
+        <v>712366.01</v>
       </c>
     </row>
     <row r="93">
@@ -15231,7 +15231,7 @@
         <v>251680000</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>167786.66</v>
+        <v>164496.73</v>
       </c>
     </row>
     <row r="94">
@@ -15252,7 +15252,7 @@
         <v>168480000</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>112320</v>
+        <v>110117.65</v>
       </c>
     </row>
   </sheetData>
